--- a/test/test_fmo_300k/plot/multiset_64bd_imag.xlsx
+++ b/test/test_fmo_300k/plot/multiset_64bd_imag.xlsx
@@ -418,5798 +418,5798 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>9.999999997745653e-21</v>
+        <v>9.528166675318398e-21</v>
       </c>
       <c r="B1" t="n">
-        <v>1.000000000010756e-20</v>
+        <v>4.112329245414952e-21</v>
       </c>
       <c r="C1" t="n">
-        <v>9.999999999651567e-21</v>
+        <v>3.054323967888998e-20</v>
       </c>
       <c r="D1" t="n">
-        <v>1.000000000000004</v>
+        <v>1</v>
       </c>
       <c r="E1" t="n">
-        <v>9.999999997790959e-21</v>
+        <v>1.0180605449117e-20</v>
       </c>
       <c r="F1" t="n">
-        <v>9.999999997847422e-21</v>
+        <v>2.387451921967247e-20</v>
       </c>
       <c r="G1" t="n">
-        <v>9.99999999768906e-21</v>
+        <v>3.877656787004035e-21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5.287741955690155e-05</v>
+        <v>5.29812778454848e-05</v>
       </c>
       <c r="B2" t="n">
-        <v>2.59600221026562e-05</v>
+        <v>2.601932779616662e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.948921808024614e-05</v>
+        <v>1.957813670958667e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9947283869271494</v>
+        <v>0.9947178144535354</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005077762617088455</v>
+        <v>0.005087874681367214</v>
       </c>
       <c r="F2" t="n">
-        <v>1.92196779039561e-05</v>
+        <v>1.926701417724252e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>7.630411811478777e-05</v>
+        <v>7.646510856916494e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.0002091821565064581</v>
+        <v>0.000210028228645237</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0001033716133394344</v>
+        <v>0.0001038518342050947</v>
       </c>
       <c r="C3" t="n">
-        <v>8.24999480098045e-05</v>
+        <v>8.358677437366329e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9791748526963827</v>
+        <v>0.9790494031987551</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02004794091157562</v>
+        <v>0.02016932005307777</v>
       </c>
       <c r="F3" t="n">
-        <v>7.825335192396288e-05</v>
+        <v>7.867273180265619e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003038993222548004</v>
+        <v>0.0003051371791405169</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0004628952247567426</v>
+        <v>0.0004655616286455021</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0002313193670760229</v>
+        <v>0.0002328781659209737</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000202265941379054</v>
+        <v>0.0002072246466194722</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9539114084394239</v>
+        <v>0.9535210053956462</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04433040807167207</v>
+        <v>0.04470664782574987</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001812644210719421</v>
+        <v>0.0001828625359539775</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006804385346182045</v>
+        <v>0.0006838198014639251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0008043927363621351</v>
+        <v>0.0008104856951794175</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0004083586118835838</v>
+        <v>0.0004121738532059664</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000398727954242461</v>
+        <v>0.0004136869293202863</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9199549020228486</v>
+        <v>0.9189825055059692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07689776631193063</v>
+        <v>0.07783358470697824</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0003344870258352927</v>
+        <v>0.0003390033995180764</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001201365336883499</v>
+        <v>0.001208559909828767</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.001220461538449456</v>
+        <v>0.001232543270537562</v>
       </c>
       <c r="B6" t="n">
-        <v>0.000632895658125166</v>
+        <v>0.0006406543810978687</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006956615098137934</v>
+        <v>0.000731245278089098</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8786388277197613</v>
+        <v>0.8765644940489564</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1164079742839053</v>
+        <v>0.1184017588901951</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000545190733678343</v>
+        <v>0.0005559653717214399</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001858988556279684</v>
+        <v>0.001873338759402362</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.001695359276732366</v>
+        <v>0.001716804756631482</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0009032661694111344</v>
+        <v>0.0009172607676332494</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001117191143701131</v>
+        <v>0.001189760798282909</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8315167276034534</v>
+        <v>0.8276247347798573</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1613041528299769</v>
+        <v>0.1650384454862467</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008204733662947512</v>
+        <v>0.0008432683558771989</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002642829610418485</v>
+        <v>0.002669725055470924</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.002211650157277268</v>
+        <v>0.002246280392915022</v>
       </c>
       <c r="B8" t="n">
-        <v>0.001217990990083546</v>
+        <v>0.001241144412329454</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001684345544830807</v>
+        <v>0.001817052938349369</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7802792742309771</v>
+        <v>0.7736865189137743</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2099013216741409</v>
+        <v>0.2162125438023824</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00116607840197713</v>
+        <v>0.001209871722663125</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003539339000703493</v>
+        <v>0.003586587817586182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.002751139644012877</v>
+        <v>0.002802657322190174</v>
       </c>
       <c r="B9" t="n">
-        <v>0.00157607557788551</v>
+        <v>0.001611821858211774</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002412178823018318</v>
+        <v>0.002635590536472212</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7266635540151849</v>
+        <v>0.7163727941627575</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2604798440147755</v>
+        <v>0.2703042609513128</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001585281657339848</v>
+        <v>0.001662925455857552</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004531926267786784</v>
+        <v>0.004609949713198058</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.003295830560038217</v>
+        <v>0.003367139517316476</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001977078546435172</v>
+        <v>0.002029286409816885</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003307839110990181</v>
+        <v>0.003659889059217055</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6723714454286903</v>
+        <v>0.6573400466395788</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3113684293399936</v>
+        <v>0.3256740002322779</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002078068238984473</v>
+        <v>0.002206592214943875</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005601308774855819</v>
+        <v>0.005723045926849154</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.003828968339191087</v>
+        <v>0.003921349622605527</v>
       </c>
       <c r="B11" t="n">
-        <v>0.002421100828879582</v>
+        <v>0.0024940484637972</v>
       </c>
       <c r="C11" t="n">
-        <v>0.004369623498540197</v>
+        <v>0.004894885453478223</v>
       </c>
       <c r="D11" t="n">
-        <v>0.618998282057142</v>
+        <v>0.5982152449239033</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3610152674758672</v>
+        <v>0.3807267993791946</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002640606839764203</v>
+        <v>0.002841047328483299</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006726150960602407</v>
+        <v>0.006906624828537461</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.004335957199649704</v>
+        <v>0.004448259936928395</v>
       </c>
       <c r="B12" t="n">
-        <v>0.002908718037742625</v>
+        <v>0.003007076039900599</v>
       </c>
       <c r="C12" t="n">
-        <v>0.005587174748636403</v>
+        <v>0.006335430352680898</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5679757089963802</v>
+        <v>0.5405386350482074</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4080434612655788</v>
+        <v>0.4339693552313829</v>
       </c>
       <c r="F12" t="n">
-        <v>0.003265073011682006</v>
+        <v>0.003561767214246831</v>
       </c>
       <c r="G12" t="n">
-        <v>0.007883906740337364</v>
+        <v>0.008139476176652704</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.004805132903256049</v>
+        <v>0.004933087903754465</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00344072733619944</v>
+        <v>0.003569639367151166</v>
       </c>
       <c r="C13" t="n">
-        <v>0.006942707715392977</v>
+        <v>0.007966877174315965</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5205307153873234</v>
+        <v>0.4857141247784732</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4512888451926491</v>
+        <v>0.4840579109071322</v>
       </c>
       <c r="F13" t="n">
-        <v>0.003939934105504422</v>
+        <v>0.004359196978975511</v>
       </c>
       <c r="G13" t="n">
-        <v>0.009051937359666331</v>
+        <v>0.009399162890197481</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.005228357441198542</v>
+        <v>0.00536409686537036</v>
       </c>
       <c r="B14" t="n">
-        <v>0.004017881601063786</v>
+        <v>0.004183042287715591</v>
       </c>
       <c r="C14" t="n">
-        <v>0.00841282555541707</v>
+        <v>0.009766601381943298</v>
       </c>
       <c r="D14" t="n">
-        <v>0.477658593000405</v>
+        <v>0.4349688105849567</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4898233404917707</v>
+        <v>0.5298356889744805</v>
       </c>
       <c r="F14" t="n">
-        <v>0.004650477082316036</v>
+        <v>0.005218858387448321</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01020852482783379</v>
+        <v>0.01066290151808523</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.005601394609781991</v>
+        <v>0.00573324529272822</v>
       </c>
       <c r="B15" t="n">
-        <v>0.004640546291818148</v>
+        <v>0.004848253277402331</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0099709503156333</v>
+        <v>0.01170623766366029</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4401093340987312</v>
+        <v>0.3893226130164515</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5229642615314235</v>
+        <v>0.5703592334975965</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005379731750467843</v>
+        <v>0.006121913814808823</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0113337814021362</v>
+        <v>0.01190850343735191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.005924011448429103</v>
+        <v>0.006036637917391555</v>
       </c>
       <c r="B16" t="n">
-        <v>0.005308326184465828</v>
+        <v>0.005565459081333888</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01158967312893747</v>
+        <v>0.01375430811793951</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4083850032461588</v>
+        <v>0.3495671804750381</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5502729578250802</v>
+        <v>0.6049149231086871</v>
       </c>
       <c r="F16" t="n">
-        <v>0.006109554629624026</v>
+        <v>0.007046184640661904</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01241047353729971</v>
+        <v>0.01311530665894778</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.006199822964055301</v>
+        <v>0.006274733609082674</v>
       </c>
       <c r="B17" t="n">
-        <v>0.006019756875639492</v>
+        <v>0.00633358178817036</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01324297971104462</v>
+        <v>0.01587892141821089</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3827477436605596</v>
+        <v>0.3162552804930189</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5715431007476768</v>
+        <v>0.6330249313189442</v>
       </c>
       <c r="F17" t="n">
-        <v>0.006821934895449387</v>
+        <v>0.007967533508825682</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01342466114559246</v>
+        <v>0.01426501786374706</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.006435825968734162</v>
+        <v>0.006452295929447684</v>
       </c>
       <c r="B18" t="n">
-        <v>0.006772038177663121</v>
+        <v>0.007149804287442231</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01490813211503732</v>
+        <v>0.01805027034882139</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3632336057565623</v>
+        <v>0.2896993988012413</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5867841050726756</v>
+        <v>0.6544443279772834</v>
       </c>
       <c r="F18" t="n">
-        <v>0.007500201314067877</v>
+        <v>0.008861506129613807</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01436609159526257</v>
+        <v>0.01534239652615052</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.006641780176137691</v>
+        <v>0.006578085374772016</v>
       </c>
       <c r="B19" t="n">
-        <v>0.007560740767881787</v>
+        <v>0.008009149150162624</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01656683814944549</v>
+        <v>0.02024270136497404</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3496757479837783</v>
+        <v>0.2699789062284246</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5961963732556531</v>
+        <v>0.6691503179651608</v>
       </c>
       <c r="F19" t="n">
-        <v>0.008130212100488216</v>
+        <v>0.009705099834074199</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01522830756661806</v>
+        <v>0.01633574008243229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.006829424423211063</v>
+        <v>0.00666430647331761</v>
       </c>
       <c r="B20" t="n">
-        <v>0.008379777756717473</v>
+        <v>0.008904180121805832</v>
       </c>
       <c r="C20" t="n">
-        <v>0.01820613271464403</v>
+        <v>0.02243615458944859</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3417318980189721</v>
+        <v>0.2569550327443515</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6001429366148098</v>
+        <v>0.6773247020817451</v>
       </c>
       <c r="F20" t="n">
-        <v>0.008701390797813709</v>
+        <v>0.01047848174453372</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01600843967383213</v>
+        <v>0.01723714224479775</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.007011592090946016</v>
+        <v>0.006725851113603062</v>
       </c>
       <c r="B21" t="n">
-        <v>0.009221399859185105</v>
+        <v>0.009824882085492271</v>
       </c>
       <c r="C21" t="n">
-        <v>0.01981804620874013</v>
+        <v>0.02461692254803058</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3389149721552512</v>
+        <v>0.2502924011388047</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5991196019162371</v>
+        <v>0.6793309103409311</v>
       </c>
       <c r="F21" t="n">
-        <v>0.009207466590517119</v>
+        <v>0.01116650979120082</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01670692117912726</v>
+        <v>0.01804252298193767</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.007201347498320847</v>
+        <v>0.006779394456622674</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01007637779989019</v>
+        <v>0.01075874273285314</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02139933539211586</v>
+        <v>0.02677773757984873</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3406258940550926</v>
+        <v>0.2494857114360324</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5937231277986175</v>
+        <v>0.6756870762058771</v>
       </c>
       <c r="F22" t="n">
-        <v>0.009646821158533193</v>
+        <v>0.01175988759089875</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01732709629743661</v>
+        <v>0.01875144999786705</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.007411152801426207</v>
+        <v>0.006842399968967129</v>
       </c>
       <c r="B23" t="n">
-        <v>0.01093441546212302</v>
+        <v>0.01169106920592457</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02295062354130281</v>
+        <v>0.02891723229001992</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3461869268934046</v>
+        <v>0.2538901819026949</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5846197596619328</v>
+        <v>0.6670364715343664</v>
       </c>
       <c r="F23" t="n">
-        <v>0.01002250643128165</v>
+        <v>0.01225587062516539</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01787461520851895</v>
+        <v>0.01936677447286214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.00765210703155</v>
+        <v>0.006932109661341448</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0117846018185415</v>
+        <v>0.01260552140612708</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02447541793337972</v>
+        <v>0.03103891110358418</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3548742598487323</v>
+        <v>0.2627542571747071</v>
       </c>
       <c r="E24" t="n">
-        <v>0.572514946573618</v>
+        <v>0.6541166319522655</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01034188219540832</v>
+        <v>0.01265843412869911</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01835678459877017</v>
+        <v>0.01989413457327551</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.007933373656319164</v>
+        <v>0.007064579522451799</v>
       </c>
       <c r="B25" t="n">
-        <v>0.01261588532305364</v>
+        <v>0.01348484572029214</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02597891153822219</v>
+        <v>0.03314976740810041</v>
       </c>
       <c r="D25" t="n">
-        <v>0.365948309879465</v>
+        <v>0.2752531875240989</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5581254823797093</v>
+        <v>0.6377283446231967</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01061593985570659</v>
+        <v>0.0129779044042855</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01878209736754292</v>
+        <v>0.02034137079757441</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.008261787166457179</v>
+        <v>0.00725382811325314</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01341771184656231</v>
+        <v>0.01431175606291218</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02746675181904957</v>
+        <v>0.03525873838647406</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3786803302080898</v>
+        <v>0.2905221341488792</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5421552611557684</v>
+        <v>0.6187055470048801</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01085847936547129</v>
+        <v>0.01323009243350066</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01915967843861062</v>
+        <v>0.02071790385010043</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.008641630385979964</v>
+        <v>0.007511139966512119</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01418069831396914</v>
+        <v>0.01506989510513661</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02894401521712369</v>
+        <v>0.03737514548840645</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3923758374838579</v>
+        <v>0.3076877083964762</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5252740299314707</v>
+        <v>0.5978869669746467</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01108502733425659</v>
+        <v>0.01343503019349106</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01949876133333606</v>
+        <v>0.02103411387533063</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.009074532586147132</v>
+        <v>0.007844562143473793</v>
       </c>
       <c r="B28" t="n">
-        <v>0.01489716860892175</v>
+        <v>0.01574479723966277</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03041450790909907</v>
+        <v>0.03950727762754157</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4063946271755035</v>
+        <v>0.3258970131921114</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5080993551648461</v>
+        <v>0.5760901805696685</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01131158361319252</v>
+        <v>0.01361541037518756</v>
       </c>
       <c r="G28" t="n">
-        <v>0.019808224942297</v>
+        <v>0.02130075885235455</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.009559567126004451</v>
+        <v>0.008258614213645404</v>
       </c>
       <c r="B29" t="n">
-        <v>0.01556155479695522</v>
+        <v>0.01632477518615858</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03188025724087196</v>
+        <v>0.04166122959954788</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4201655889054145</v>
+        <v>0.3443435544023442</v>
       </c>
       <c r="E29" t="n">
-        <v>0.49118314754082</v>
+        <v>0.5540884543298183</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01155353859186807</v>
+        <v>0.01379491120020622</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02009634579806225</v>
+        <v>0.02152846106827963</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.01009352118102337</v>
+        <v>0.008754209983359329</v>
       </c>
       <c r="B30" t="n">
-        <v>0.01617066825270808</v>
+        <v>0.01680165367220104</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03334121860297629</v>
+        <v>0.04384009014431026</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4331973464136145</v>
+        <v>0.3622895032434135</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4750017876776548</v>
+        <v>0.5325907259843634</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01182484274348236</v>
+        <v>0.01399653871494147</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02037061512854401</v>
+        <v>0.02172727825741092</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.01067124154473515</v>
+        <v>0.009328780546460618</v>
       </c>
       <c r="B31" t="n">
-        <v>0.01672385325124997</v>
+        <v>0.01717128525405226</v>
       </c>
       <c r="C31" t="n">
-        <v>0.03479533103105312</v>
+        <v>0.04604351053816283</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4450854775006739</v>
+        <v>0.3790839565897704</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4599493602547743</v>
+        <v>0.5122249585532584</v>
       </c>
       <c r="F31" t="n">
-        <v>0.01213718692056643</v>
+        <v>0.01424113940314706</v>
       </c>
       <c r="G31" t="n">
-        <v>0.02063754949694648</v>
+        <v>0.02190636911514825</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.01128605432231076</v>
+        <v>0.009976575739215898</v>
       </c>
       <c r="B32" t="n">
-        <v>0.01722296410278877</v>
+        <v>0.01743380736545527</v>
       </c>
       <c r="C32" t="n">
-        <v>0.03623876276626083</v>
+        <v>0.0482676643968557</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4555157943347489</v>
+        <v>0.3941769626522227</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4463344150256099</v>
+        <v>0.4935250473500788</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01249939349796091</v>
+        <v>0.01454618734526118</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02090261595032672</v>
+        <v>0.02207375515091037</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.01193022034788758</v>
+        <v>0.01068910817935955</v>
       </c>
       <c r="B33" t="n">
-        <v>0.01767213433413016</v>
+        <v>0.01759362187742431</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03766633583261996</v>
+        <v>0.05050555356391671</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4642641590081805</v>
+        <v>0.407129166506577</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4343797199130751</v>
+        <v>0.4769214337983663</v>
       </c>
       <c r="F33" t="n">
-        <v>0.01291716597052501</v>
+        <v>0.01492494219145633</v>
       </c>
       <c r="G33" t="n">
-        <v>0.02117026459358382</v>
+        <v>0.02223617388289959</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.01259537435890131</v>
+        <v>0.01145569977714892</v>
       </c>
       <c r="B34" t="n">
-        <v>0.01807740637503391</v>
+        <v>0.01765909949060139</v>
       </c>
       <c r="C34" t="n">
-        <v>0.03907208397335772</v>
+        <v>0.05274761581980713</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4711935879137799</v>
+        <v>0.4176171091414272</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4242244465178257</v>
+        <v>0.46273545869383</v>
       </c>
       <c r="F34" t="n">
-        <v>0.01339311196652097</v>
+        <v>0.01538600309559728</v>
       </c>
       <c r="G34" t="n">
-        <v>0.02144398889458461</v>
+        <v>0.02239901398158819</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.01327296665660025</v>
+        <v>0.01226408923712647</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01844626197891592</v>
+        <v>0.01764203785696095</v>
       </c>
       <c r="C35" t="n">
-        <v>0.04044980160953272</v>
+        <v>0.05498253610489037</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4762485359193357</v>
+        <v>0.425434335516545</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4159290381659572</v>
+        <v>0.4511774129650566</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01392699475839461</v>
+        <v>0.01593326467751002</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02172640091126652</v>
+        <v>0.02256632364191067</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.01395467656888082</v>
+        <v>0.01310105864072991</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01878708930801013</v>
+        <v>0.01755692392708998</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0417935865935674</v>
+        <v>0.05719817696228628</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4794468063064329</v>
+        <v>0.4304885465354018</v>
       </c>
       <c r="E36" t="n">
-        <v>0.409482340716971</v>
+        <v>0.4423481935517947</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01451617316586993</v>
+        <v>0.01656622181939666</v>
       </c>
       <c r="G36" t="n">
-        <v>0.02201932734025794</v>
+        <v>0.02274087856330104</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.01463273389162563</v>
+        <v>0.01395304414346662</v>
       </c>
       <c r="B37" t="n">
-        <v>0.01910863578683392</v>
+        <v>0.01742006329565456</v>
       </c>
       <c r="C37" t="n">
-        <v>0.04309827235427607</v>
+        <v>0.05938252227124399</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4808702090170135</v>
+        <v>0.4327951164306144</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4048100468366715</v>
+        <v>0.4362443933619603</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01515616438756436</v>
+        <v>0.01728056366632583</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02232393772600602</v>
+        <v>0.02292429683073415</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.01530018039599978</v>
+        <v>0.01480670330744836</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01941951557545861</v>
+        <v>0.0172486460432704</v>
       </c>
       <c r="C38" t="n">
-        <v>0.04435972715252507</v>
+        <v>0.0615245611494681</v>
       </c>
       <c r="D38" t="n">
-        <v>0.480653564869944</v>
+        <v>0.4324673921753419</v>
       </c>
       <c r="E38" t="n">
-        <v>0.40178499616326</v>
+        <v>0.4327665607702583</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01584117326752387</v>
+        <v>0.01806894759270749</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02264084257527909</v>
+        <v>0.02311718896150538</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.015951069041837</v>
+        <v>0.01564941359007089</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01972777067689206</v>
+        <v>0.01705982009117602</v>
       </c>
       <c r="C39" t="n">
-        <v>0.04557509457558851</v>
+        <v>0.063615024172303</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4789725629686427</v>
+        <v>0.429704309845042</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4002387308006958</v>
+        <v>0.4317302258731826</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01656459004527712</v>
+        <v>0.01892187417439727</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0229701818910642</v>
+        <v>0.02331933225382864</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.01658058462875694</v>
+        <v>0.01646968530973623</v>
       </c>
       <c r="B40" t="n">
-        <v>0.02004049951659228</v>
+        <v>0.01686983740258886</v>
       </c>
       <c r="C40" t="n">
-        <v>0.04674297102591549</v>
+        <v>0.06564692986787803</v>
       </c>
       <c r="D40" t="n">
-        <v>0.4760313510404947</v>
+        <v>0.424775925796213</v>
       </c>
       <c r="E40" t="n">
-        <v>0.3999733862670837</v>
+        <v>0.4328791961356044</v>
       </c>
       <c r="F40" t="n">
-        <v>0.01731949430532136</v>
+        <v>0.01982856600878747</v>
       </c>
       <c r="G40" t="n">
-        <v>0.02331171321583536</v>
+        <v>0.02352985947919174</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.01718510190885242</v>
+        <v>0.01725748049151052</v>
       </c>
       <c r="B41" t="n">
-        <v>0.02036356763725496</v>
+        <v>0.016693325126398</v>
       </c>
       <c r="C41" t="n">
-        <v>0.04786332819543911</v>
+        <v>0.06761590732813848</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4720506326208833</v>
+        <v>0.4180075012374352</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4007733972451654</v>
+        <v>0.4359005570772169</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01809905038217796</v>
+        <v>0.02077777752598758</v>
       </c>
       <c r="G41" t="n">
-        <v>0.02366492201022609</v>
+        <v>0.02374745121331361</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.01776219970006149</v>
+        <v>0.0180044364637383</v>
       </c>
       <c r="B42" t="n">
-        <v>0.02070144247262431</v>
+        <v>0.01654272046727766</v>
       </c>
       <c r="C42" t="n">
-        <v>0.04893735863651056</v>
+        <v>0.06952029423580933</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4672568689137079</v>
+        <v>0.4097628034599681</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4024161957656213</v>
+        <v>0.440440747609499</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01889683385871831</v>
+        <v>0.02175847508408667</v>
       </c>
       <c r="G42" t="n">
-        <v>0.02402910065275234</v>
+        <v>0.02397052267962079</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.01831061956196876</v>
+        <v>0.01870399789852696</v>
       </c>
       <c r="B43" t="n">
-        <v>0.02105715086513133</v>
+        <v>0.01642789087374791</v>
       </c>
       <c r="C43" t="n">
-        <v>0.04996739111015815</v>
+        <v>0.07136102771775477</v>
       </c>
       <c r="D43" t="n">
-        <v>0.461872847092635</v>
+        <v>0.4004272845317404</v>
       </c>
       <c r="E43" t="n">
-        <v>0.4046815877099494</v>
+        <v>0.4461220466172684</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01970700477309893</v>
+        <v>0.02276035558575755</v>
       </c>
       <c r="G43" t="n">
-        <v>0.02440339888706563</v>
+        <v>0.02419739677520411</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.01883018402954797</v>
+        <v>0.0193514640919552</v>
       </c>
       <c r="B44" t="n">
-        <v>0.02143232015848921</v>
+        <v>0.01635594299889467</v>
       </c>
       <c r="C44" t="n">
-        <v>0.05095669105845252</v>
+        <v>0.07314136229934913</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4561102809520018</v>
+        <v>0.3903917855919929</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4073592555204948</v>
+        <v>0.4525587964094754</v>
       </c>
       <c r="F44" t="n">
-        <v>0.02052438527507311</v>
+        <v>0.02377419261650457</v>
       </c>
       <c r="G44" t="n">
-        <v>0.02478688300593608</v>
+        <v>0.02442645599182837</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.01932168650668538</v>
+        <v>0.01994396156497621</v>
       </c>
       <c r="B45" t="n">
-        <v>0.02182732709314172</v>
+        <v>0.01633120979408632</v>
       </c>
       <c r="C45" t="n">
-        <v>0.05190916880558782</v>
+        <v>0.07486646307140712</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4501644023638212</v>
+        <v>0.3800373526882022</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4102543455955355</v>
+        <v>0.4593727220478104</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0213445022082893</v>
+        <v>0.0247920221463208</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02517856742693215</v>
+        <v>0.02465626868719707</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.01978675300855924</v>
+        <v>0.02048035394136932</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0222414855745242</v>
+        <v>0.01635539205481363</v>
       </c>
       <c r="C46" t="n">
-        <v>0.05282913190421768</v>
+        <v>0.07654292430820521</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4442101265377512</v>
+        <v>0.3697216650033585</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4131914850361594</v>
+        <v>0.4662067858237758</v>
       </c>
       <c r="F46" t="n">
-        <v>0.02216356754763748</v>
+        <v>0.02580719401045126</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02557745039115648</v>
+        <v>0.02488568485802613</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.02022768225262564</v>
+        <v>0.02096110269886072</v>
       </c>
       <c r="B47" t="n">
-        <v>0.02267325187618419</v>
+        <v>0.01642782323615928</v>
       </c>
       <c r="C47" t="n">
-        <v>0.05372104580754095</v>
+        <v>0.07817826128879356</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4383994754920488</v>
+        <v>0.3597674839755637</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4160175840021922</v>
+        <v>0.4727371078548641</v>
       </c>
       <c r="F47" t="n">
-        <v>0.02297841083939856</v>
+        <v>0.02681432332177809</v>
       </c>
       <c r="G47" t="n">
-        <v>0.02598254973000939</v>
+        <v>0.02511389762398063</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.02064728365720661</v>
+        <v>0.02138809291153397</v>
       </c>
       <c r="B48" t="n">
-        <v>0.02312046783228065</v>
+        <v>0.01654582259377115</v>
       </c>
       <c r="C48" t="n">
-        <v>0.05458928768038036</v>
+        <v>0.07978041915259809</v>
       </c>
       <c r="D48" t="n">
-        <v>0.432860432762144</v>
+        <v>0.350453410219691</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4186032180712938</v>
+        <v>0.4786826045188988</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02378638777158506</v>
+        <v>0.02780918031364159</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02639292222510396</v>
+        <v>0.02534047028986561</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.02104871082075138</v>
+        <v>0.02176443524207958</v>
       </c>
       <c r="B49" t="n">
-        <v>0.02358060549283682</v>
+        <v>0.01670510044429564</v>
       </c>
       <c r="C49" t="n">
-        <v>0.05543792319658962</v>
+        <v>0.0813573325547754</v>
       </c>
       <c r="D49" t="n">
-        <v>0.4276967012474268</v>
+        <v>0.3420071729930149</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4208430890899001</v>
+        <v>0.4838120777819597</v>
       </c>
       <c r="F49" t="n">
-        <v>0.02458529652672003</v>
+        <v>0.02878855227172371</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02680767362576477</v>
+        <v>0.0255653287121515</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.02143529847417916</v>
+        <v>0.02209425332137014</v>
       </c>
       <c r="B50" t="n">
-        <v>0.02405099329049968</v>
+        <v>0.01690018383595966</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0562705560290874</v>
+        <v>0.08291656319966596</v>
       </c>
       <c r="D50" t="n">
-        <v>0.4229878550402051</v>
+        <v>0.3346015313949452</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4226560645708275</v>
+        <v>0.4879486373992046</v>
       </c>
       <c r="F50" t="n">
-        <v>0.02537328830296264</v>
+        <v>0.02975010427509051</v>
       </c>
       <c r="G50" t="n">
-        <v>0.02722594429223126</v>
+        <v>0.02578872657376383</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.02181042637942729</v>
+        <v>0.02238246834260276</v>
       </c>
       <c r="B51" t="n">
-        <v>0.02452901147343933</v>
+        <v>0.01712483677922709</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0570902487058069</v>
+        <v>0.08446502841503192</v>
       </c>
       <c r="D51" t="n">
-        <v>0.4187898614993558</v>
+        <v>0.3283526577510165</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4239847783272033</v>
+        <v>0.4909715636242382</v>
       </c>
       <c r="F51" t="n">
-        <v>0.02614879264524099</v>
+        <v>0.03069225519245912</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02764688096952011</v>
+        <v>0.02601118989542431</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.02217741224693502</v>
+        <v>0.02263458766096573</v>
       </c>
       <c r="B52" t="n">
-        <v>0.02501225368370378</v>
+        <v>0.01737245132257489</v>
       </c>
       <c r="C52" t="n">
-        <v>0.05789950406682553</v>
+        <v>0.08600882441643336</v>
       </c>
       <c r="D52" t="n">
-        <v>0.4151357995750861</v>
+        <v>0.3233209841015072</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4247949724253016</v>
+        <v>0.4928156363269037</v>
       </c>
       <c r="F52" t="n">
-        <v>0.02691046852349523</v>
+        <v>0.03161407623401433</v>
       </c>
       <c r="G52" t="n">
-        <v>0.02806958947865073</v>
+        <v>0.02623343993760052</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.02253942492666286</v>
+        <v>0.0228565002815397</v>
       </c>
       <c r="B53" t="n">
-        <v>0.02549863213073065</v>
+        <v>0.0176363963660041</v>
       </c>
       <c r="C53" t="n">
-        <v>0.05870033879576552</v>
+        <v>0.08755313491855635</v>
       </c>
       <c r="D53" t="n">
-        <v>0.4120369885927482</v>
+        <v>0.3195142069252485</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4250743308727141</v>
+        <v>0.4934682366133951</v>
       </c>
       <c r="F53" t="n">
-        <v>0.02765718526181687</v>
+        <v>0.03251521303746627</v>
       </c>
       <c r="G53" t="n">
-        <v>0.02849309941956036</v>
+        <v>0.02645631185778971</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.02289941033368592</v>
+        <v>0.02305428735956435</v>
       </c>
       <c r="B54" t="n">
-        <v>0.02598640995990266</v>
+        <v>0.01791031548542572</v>
       </c>
       <c r="C54" t="n">
-        <v>0.05949434253999111</v>
+        <v>0.08910221365877916</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4094840941451511</v>
+        <v>0.3168920718519149</v>
       </c>
       <c r="E54" t="n">
-        <v>0.424831346256943</v>
+        <v>0.4929646148472563</v>
       </c>
       <c r="F54" t="n">
-        <v>0.02838803372624494</v>
+        <v>0.03339582445959247</v>
       </c>
       <c r="G54" t="n">
-        <v>0.02891636303806995</v>
+        <v>0.02668067233746726</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.02326003423250703</v>
+        <v>0.02323404736394487</v>
       </c>
       <c r="B55" t="n">
-        <v>0.02647418766743275</v>
+        <v>0.01818836777161636</v>
       </c>
       <c r="C55" t="n">
-        <v>0.06028271478524285</v>
+        <v>0.09065942259365038</v>
       </c>
       <c r="D55" t="n">
-        <v>0.407448724038689</v>
+        <v>0.3153726829089604</v>
       </c>
       <c r="E55" t="n">
-        <v>0.424093711327373</v>
+        <v>0.4913816091208065</v>
       </c>
       <c r="F55" t="n">
-        <v>0.02910234393461669</v>
+        <v>0.03425652943308505</v>
       </c>
       <c r="G55" t="n">
-        <v>0.02933828401413931</v>
+        <v>0.02690734080793686</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.02362364524888979</v>
+        <v>0.02340173758330193</v>
       </c>
       <c r="B56" t="n">
-        <v>0.02696089624147792</v>
+        <v>0.01846541216461071</v>
       </c>
       <c r="C56" t="n">
-        <v>0.06106635547887565</v>
+        <v>0.09222730599107118</v>
       </c>
       <c r="D56" t="n">
-        <v>0.4058861006617839</v>
+        <v>0.3148399010270306</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4229055613290003</v>
+        <v>0.4888302690017501</v>
       </c>
       <c r="F56" t="n">
-        <v>0.02979970336533984</v>
+        <v>0.03509835172788856</v>
       </c>
       <c r="G56" t="n">
-        <v>0.02975773767463103</v>
+        <v>0.02713702250434688</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.02399225099401443</v>
+        <v>0.02356303387175793</v>
       </c>
       <c r="B57" t="n">
-        <v>0.02744578601414182</v>
+        <v>0.01873713775628627</v>
       </c>
       <c r="C57" t="n">
-        <v>0.06184599266616488</v>
+        <v>0.09380768318323032</v>
       </c>
       <c r="D57" t="n">
-        <v>0.404738702137547</v>
+        <v>0.3151513955551864</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4213237248280488</v>
+        <v>0.4854478390371831</v>
       </c>
       <c r="F57" t="n">
-        <v>0.03047995395356164</v>
+        <v>0.03592265336365933</v>
       </c>
       <c r="G57" t="n">
-        <v>0.03017358940652047</v>
+        <v>0.0273702572326964</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.02436750913861999</v>
+        <v>0.02372320930295167</v>
       </c>
       <c r="B58" t="n">
-        <v>0.02792838608923816</v>
+        <v>0.0190001435098438</v>
       </c>
       <c r="C58" t="n">
-        <v>0.06262230011912971</v>
+        <v>0.09540174449967923</v>
       </c>
       <c r="D58" t="n">
-        <v>0.4039404287585899</v>
+        <v>0.316146936762365</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4194134683053876</v>
+        <v>0.4813895282466585</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0311431579853993</v>
+        <v>0.036731051544896</v>
       </c>
       <c r="G58" t="n">
-        <v>0.03058474960364887</v>
+        <v>0.02760738613360554</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.02475072587499602</v>
+        <v>0.02388703266604502</v>
       </c>
       <c r="B59" t="n">
-        <v>0.02840844351353999</v>
+        <v>0.01925197168225</v>
       </c>
       <c r="C59" t="n">
-        <v>0.06339594395741853</v>
+        <v>0.0970101384454881</v>
       </c>
       <c r="D59" t="n">
-        <v>0.4034213283544364</v>
+        <v>0.3176565551148908</v>
       </c>
       <c r="E59" t="n">
-        <v>0.417243748755336</v>
+        <v>0.4768204465991576</v>
       </c>
       <c r="F59" t="n">
-        <v>0.03178955328629821</v>
+        <v>0.03752531886366563</v>
       </c>
       <c r="G59" t="n">
-        <v>0.03099025625798283</v>
+        <v>0.02784853662850309</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.02514284614851454</v>
+        <v>0.02405868765713221</v>
       </c>
       <c r="B60" t="n">
-        <v>0.02888585361685278</v>
+        <v>0.01949110001725394</v>
       </c>
       <c r="C60" t="n">
-        <v>0.06416754224098636</v>
+        <v>0.09863304226608159</v>
       </c>
       <c r="D60" t="n">
-        <v>0.4031128633271397</v>
+        <v>0.3195082500957684</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4148820209823508</v>
+        <v>0.4719080244224436</v>
       </c>
       <c r="F60" t="n">
-        <v>0.03241952438078603</v>
+        <v>0.03830727081200141</v>
       </c>
       <c r="G60" t="n">
-        <v>0.03138934930336965</v>
+        <v>0.02809362472931876</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.02554445476769884</v>
+        <v>0.02424171308709217</v>
       </c>
       <c r="B61" t="n">
-        <v>0.02936059440634549</v>
+        <v>0.01971689792081886</v>
       </c>
       <c r="C61" t="n">
-        <v>0.06493758567010305</v>
+        <v>0.1002702119835395</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4029525938738121</v>
+        <v>0.3215349815547124</v>
       </c>
       <c r="E61" t="n">
-        <v>0.4123896792575811</v>
+        <v>0.4668151758706519</v>
       </c>
       <c r="F61" t="n">
-        <v>0.03303356700393952</v>
+        <v>0.03907864734453741</v>
       </c>
       <c r="G61" t="n">
-        <v>0.03178152502051024</v>
+        <v>0.02834237223864797</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.02595578673703745</v>
+        <v>0.02443896433491122</v>
       </c>
       <c r="B62" t="n">
-        <v>0.02983267193570592</v>
+        <v>0.01992955155132795</v>
       </c>
       <c r="C62" t="n">
-        <v>0.06570634671788393</v>
+        <v>0.1019210127442741</v>
       </c>
       <c r="D62" t="n">
-        <v>0.4028872096929615</v>
+        <v>0.323580724079443</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4098191701080907</v>
+        <v>0.4616944153035255</v>
       </c>
       <c r="F62" t="n">
-        <v>0.03363224169246258</v>
+        <v>0.03984099731435119</v>
       </c>
       <c r="G62" t="n">
-        <v>0.03216657311585713</v>
+        <v>0.02859433467216674</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.02637674281048298</v>
+        <v>0.02465259625772982</v>
       </c>
       <c r="B63" t="n">
-        <v>0.03030207525192584</v>
+        <v>0.02012996285217461</v>
       </c>
       <c r="C63" t="n">
-        <v>0.06647379464713549</v>
+        <v>0.1035844332203678</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4028736315778762</v>
+        <v>0.3255054256073298</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4072130509526433</v>
+        <v>0.4566830706843334</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03421612412498281</v>
+        <v>0.04059557571849394</v>
       </c>
       <c r="G63" t="n">
-        <v>0.03254458063495725</v>
+        <v>0.02884893565957063</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.02680691945626482</v>
+        <v>0.02488406719025517</v>
       </c>
       <c r="B64" t="n">
-        <v>0.03076873180934479</v>
+        <v>0.02031962812629772</v>
       </c>
       <c r="C64" t="n">
-        <v>0.06723954494939437</v>
+        <v>0.1052590893382771</v>
       </c>
       <c r="D64" t="n">
-        <v>0.4028783650242596</v>
+        <v>0.3271887827936745</v>
       </c>
       <c r="E64" t="n">
-        <v>0.4046047686567197</v>
+        <v>0.4518996652976277</v>
       </c>
       <c r="F64" t="n">
-        <v>0.03478576561832991</v>
+        <v>0.04134326311000318</v>
       </c>
       <c r="G64" t="n">
-        <v>0.03291590448567912</v>
+        <v>0.02910550414386458</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.02724564343884637</v>
+        <v>0.02513416284967683</v>
       </c>
       <c r="B65" t="n">
-        <v>0.03123246387716755</v>
+        <v>0.02050050232839595</v>
       </c>
       <c r="C65" t="n">
-        <v>0.06800285513346907</v>
+        <v>0.1069432232271037</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4028753718321077</v>
+        <v>0.3285328125131441</v>
       </c>
       <c r="E65" t="n">
-        <v>0.402020857450173</v>
+        <v>0.4474414733750781</v>
       </c>
       <c r="F65" t="n">
-        <v>0.03534167318530009</v>
+        <v>0.0420845144416245</v>
       </c>
       <c r="G65" t="n">
-        <v>0.03328113508292285</v>
+        <v>0.0293633112649766</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.02769200057393891</v>
+        <v>0.02540303841921571</v>
       </c>
       <c r="B66" t="n">
-        <v>0.03169296354667724</v>
+        <v>0.02067485555371881</v>
       </c>
       <c r="C66" t="n">
-        <v>0.06876269423296209</v>
+        <v>0.108634704618623</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4028432842965336</v>
+        <v>0.3294632522139676</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3994837036334202</v>
+        <v>0.4433832037396459</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0358843011862458</v>
+        <v>0.04281934129444803</v>
       </c>
       <c r="G66" t="n">
-        <v>0.03364105253020726</v>
+        <v>0.02962160416038064</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.02814486909284918</v>
+        <v>0.02569027667546716</v>
       </c>
       <c r="B67" t="n">
-        <v>0.03214978457787145</v>
+        <v>0.02084512807888125</v>
       </c>
       <c r="C67" t="n">
-        <v>0.06951785763207441</v>
+        <v>0.1103310443115253</v>
       </c>
       <c r="D67" t="n">
-        <v>0.4027629095020417</v>
+        <v>0.3299298704005585</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3970139464288673</v>
+        <v>0.4397767180214635</v>
       </c>
       <c r="F67" t="n">
-        <v>0.03641405421724728</v>
+        <v>0.04354732806747888</v>
       </c>
       <c r="G67" t="n">
-        <v>0.03399657854905199</v>
+        <v>0.0298796344446255</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.02860296707757676</v>
+        <v>0.02599495949734544</v>
       </c>
       <c r="B68" t="n">
-        <v>0.03260236095440069</v>
+        <v>0.02101379024562094</v>
       </c>
       <c r="C68" t="n">
-        <v>0.07026706876312229</v>
+        <v>0.1120294272005665</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4026152093553308</v>
+        <v>0.3299058158113805</v>
       </c>
       <c r="E68" t="n">
-        <v>0.3946323834009152</v>
+        <v>0.4366516466659973</v>
       </c>
       <c r="F68" t="n">
-        <v>0.03693129224645927</v>
+        <v>0.04426768011111229</v>
       </c>
       <c r="G68" t="n">
-        <v>0.03434871820220223</v>
+        <v>0.03013668046797703</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.02906490270580752</v>
+        <v>0.02631574972697907</v>
       </c>
       <c r="B69" t="n">
-        <v>0.03305005196311357</v>
+        <v>0.02118321345086607</v>
       </c>
       <c r="C69" t="n">
-        <v>0.07100906828919849</v>
+        <v>0.1137267683206471</v>
       </c>
       <c r="D69" t="n">
-        <v>0.402380179297166</v>
+        <v>0.329386169885109</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3923609646839229</v>
+        <v>0.4340167358301104</v>
       </c>
       <c r="F69" t="n">
-        <v>0.03743634101975249</v>
+        <v>0.04497929928503783</v>
       </c>
       <c r="G69" t="n">
-        <v>0.03469849204103657</v>
+        <v>0.03039206350125026</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.02952921966704395</v>
+        <v>0.02665098015413002</v>
       </c>
       <c r="B70" t="n">
-        <v>0.03349219746337372</v>
+        <v>0.02135555785064772</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0717426790183066</v>
+        <v>0.1154197917518729</v>
       </c>
       <c r="D70" t="n">
-        <v>0.4020369392755604</v>
+        <v>0.3283858835626911</v>
       </c>
       <c r="E70" t="n">
-        <v>0.3902225837623823</v>
+        <v>0.4318617492438743</v>
       </c>
       <c r="F70" t="n">
-        <v>0.03792950628004203</v>
+        <v>0.04568087943636568</v>
       </c>
       <c r="G70" t="n">
-        <v>0.03504687453328061</v>
+        <v>0.03064515800041851</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.02999444066006115</v>
+        <v>0.02699874625821711</v>
       </c>
       <c r="B71" t="n">
-        <v>0.03392816792737072</v>
+        <v>0.02153268141104028</v>
       </c>
       <c r="C71" t="n">
-        <v>0.07246683648585762</v>
+        <v>0.1171051276590551</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4015651152015398</v>
+        <v>0.3269372529420908</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3882396177505034</v>
+        <v>0.4301597830503966</v>
       </c>
       <c r="F71" t="n">
-        <v>0.03841108044982463</v>
+        <v>0.04637101244511441</v>
       </c>
       <c r="G71" t="n">
-        <v>0.03539474152483969</v>
+        <v>0.03089539623408546</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.03045910953603379</v>
+        <v>0.02735699915610624</v>
       </c>
       <c r="B72" t="n">
-        <v>0.03435740440380009</v>
+        <v>0.02171607382725986</v>
       </c>
       <c r="C72" t="n">
-        <v>0.07318061752665826</v>
+        <v>0.1187794186269319</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4009472848736281</v>
+        <v>0.3250870499749923</v>
       </c>
       <c r="E72" t="n">
-        <v>0.3864314167997204</v>
+        <v>0.4288698944972888</v>
       </c>
       <c r="F72" t="n">
-        <v>0.03888134543383755</v>
+        <v>0.04704829556485778</v>
       </c>
       <c r="G72" t="n">
-        <v>0.03574282142632399</v>
+        <v>0.03114226835256332</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.03092182754577151</v>
+        <v>0.02772363503005835</v>
       </c>
       <c r="B73" t="n">
-        <v>0.03477944910526261</v>
+        <v>0.02190681721914321</v>
       </c>
       <c r="C73" t="n">
-        <v>0.07388326352626372</v>
+        <v>0.1204394251844938</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4001715063090002</v>
+        <v>0.3228934348586736</v>
       </c>
       <c r="E73" t="n">
-        <v>0.3848117213473685</v>
+        <v>0.4279399363490458</v>
       </c>
       <c r="F73" t="n">
-        <v>0.03934057511151155</v>
+        <v>0.04771143184549425</v>
       </c>
       <c r="G73" t="n">
-        <v>0.03609165705482076</v>
+        <v>0.03138531951309094</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.03138128313430309</v>
+        <v>0.02809657727654926</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0351939677527875</v>
+        <v>0.02210557355212419</v>
       </c>
       <c r="C74" t="n">
-        <v>0.07457417727021368</v>
+        <v>0.1220821212768577</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3992335367043431</v>
+        <v>0.3204227955705842</v>
       </c>
       <c r="E74" t="n">
-        <v>0.3833864155677514</v>
+        <v>0.4273094703963084</v>
       </c>
       <c r="F74" t="n">
-        <v>0.03978903725262889</v>
+        <v>0.04835931672752713</v>
       </c>
       <c r="G74" t="n">
-        <v>0.03644158231797419</v>
+        <v>0.03162414520004864</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.03183627264629967</v>
+        <v>0.02847384802253602</v>
       </c>
       <c r="B75" t="n">
-        <v>0.03560076185212213</v>
+        <v>0.02231259687921087</v>
       </c>
       <c r="C75" t="n">
-        <v>0.07525288788021381</v>
+        <v>0.1237047724317658</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3981385092573594</v>
+        <v>0.31774662258471</v>
       </c>
       <c r="E75" t="n">
-        <v>0.382151863089319</v>
+        <v>0.4269126689802201</v>
       </c>
       <c r="F75" t="n">
-        <v>0.04022699373543206</v>
+        <v>0.04899110582274956</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0367927115392558</v>
+        <v>0.0318583852788078</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.0322857116767653</v>
+        <v>0.02885362650837799</v>
       </c>
       <c r="B76" t="n">
-        <v>0.03599976851254261</v>
+        <v>0.02252776698009694</v>
       </c>
       <c r="C76" t="n">
-        <v>0.07591899723234874</v>
+        <v>0.1253049919580272</v>
       </c>
       <c r="D76" t="n">
-        <v>0.3969015995386228</v>
+        <v>0.3149384674074823</v>
       </c>
       <c r="E76" t="n">
-        <v>0.381094281809805</v>
+        <v>0.4266811686551685</v>
       </c>
       <c r="F76" t="n">
-        <v>0.04065470007323409</v>
+        <v>0.04960626120616475</v>
       </c>
       <c r="G76" t="n">
-        <v>0.03714494115667927</v>
+        <v>0.03208771728468225</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.03272864009579952</v>
+        <v>0.02923429299636798</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0363910482107043</v>
+        <v>0.02275063990085387</v>
       </c>
       <c r="C77" t="n">
-        <v>0.07657212388130662</v>
+        <v>0.1268807732662706</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3955472450465657</v>
+        <v>0.3120710125935203</v>
       </c>
       <c r="E77" t="n">
-        <v>0.3801905769426985</v>
+        <v>0.4265468560560016</v>
       </c>
       <c r="F77" t="n">
-        <v>0.04107240345054373</v>
+        <v>0.05020457555615622</v>
       </c>
       <c r="G77" t="n">
-        <v>0.03749796237236795</v>
+        <v>0.03231184963082959</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>0.0331642228889645</v>
+        <v>0.02961445801799741</v>
       </c>
       <c r="B78" t="n">
-        <v>0.03677476332797979</v>
+        <v>0.02298051024150157</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0772118520889271</v>
+        <v>0.1284304990240023</v>
       </c>
       <c r="D78" t="n">
-        <v>0.3941068247299926</v>
+        <v>0.3092133094395667</v>
       </c>
       <c r="E78" t="n">
-        <v>0.3794107128121535</v>
+        <v>0.4264445327060218</v>
       </c>
       <c r="F78" t="n">
-        <v>0.04148034102006752</v>
+        <v>0.05078617520074657</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0378512831319182</v>
+        <v>0.03253051537016371</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.03359174851509535</v>
+        <v>0.02999297754121106</v>
       </c>
       <c r="B79" t="n">
-        <v>0.03715115121879686</v>
+        <v>0.02321647973707296</v>
       </c>
       <c r="C79" t="n">
-        <v>0.07783769617896692</v>
+        <v>0.1299529303379517</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3926151228663758</v>
+        <v>0.3064282845574833</v>
       </c>
       <c r="E79" t="n">
-        <v>0.3787212815741569</v>
+        <v>0.4263143565372294</v>
       </c>
       <c r="F79" t="n">
-        <v>0.04187874286675457</v>
+        <v>0.05135150423996541</v>
       </c>
       <c r="G79" t="n">
-        <v>0.03820425677985152</v>
+        <v>0.03274346704908572</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0.03401062542120755</v>
+        <v>0.03036895534403533</v>
       </c>
       <c r="B80" t="n">
-        <v>0.03752049412369898</v>
+        <v>0.02345752689000924</v>
       </c>
       <c r="C80" t="n">
-        <v>0.07844908734333203</v>
+        <v>0.1314471811850051</v>
       </c>
       <c r="D80" t="n">
-        <v>0.3911061978500883</v>
+        <v>0.3037706265870241</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3780896423395566</v>
+        <v>0.4261039437770279</v>
       </c>
       <c r="F80" t="n">
-        <v>0.04226784081412201</v>
+        <v>0.05190129318721082</v>
       </c>
       <c r="G80" t="n">
-        <v>0.03855611210799979</v>
+        <v>0.03295047302968712</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.03442037702051363</v>
+        <v>0.03074173424638333</v>
       </c>
       <c r="B81" t="n">
-        <v>0.03788308807806948</v>
+        <v>0.02370257303266148</v>
       </c>
       <c r="C81" t="n">
-        <v>0.07904538610772807</v>
+        <v>0.1329126848889588</v>
       </c>
       <c r="D81" t="n">
-        <v>0.3896094476647286</v>
+        <v>0.3012851484320946</v>
       </c>
       <c r="E81" t="n">
-        <v>0.3774878363761212</v>
+        <v>0.4257700276752585</v>
       </c>
       <c r="F81" t="n">
-        <v>0.04264788172909869</v>
+        <v>0.05243651611352822</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0389059830237319</v>
+        <v>0.03315131561111518</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.03482063521301062</v>
+        <v>0.03111087812707873</v>
       </c>
       <c r="B82" t="n">
-        <v>0.03823921457470624</v>
+        <v>0.02395054113564042</v>
       </c>
       <c r="C82" t="n">
-        <v>0.07962591611531335</v>
+        <v>0.1343491584084201</v>
       </c>
       <c r="D82" t="n">
-        <v>0.3881466635464904</v>
+        <v>0.2990056993879158</v>
       </c>
       <c r="E82" t="n">
-        <v>0.3768954885148711</v>
+        <v>0.4252795912231169</v>
       </c>
       <c r="F82" t="n">
-        <v>0.04301914181674022</v>
+        <v>0.05295834060043151</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0392529402188617</v>
+        <v>0.0333457911173969</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.03521113282875127</v>
+        <v>0.03147614672131607</v>
       </c>
       <c r="B83" t="n">
-        <v>0.03858911771763181</v>
+        <v>0.02420040476901024</v>
       </c>
       <c r="C83" t="n">
-        <v>0.08019000283667703</v>
+        <v>0.1357565665862241</v>
       </c>
       <c r="D83" t="n">
-        <v>0.3867307386949021</v>
+        <v>0.2969546960837778</v>
       </c>
       <c r="E83" t="n">
-        <v>0.3763010451222895</v>
+        <v>0.4246103992989116</v>
       </c>
       <c r="F83" t="n">
-        <v>0.04338193688286807</v>
+        <v>0.05346807467340865</v>
       </c>
       <c r="G83" t="n">
-        <v>0.03959602591687762</v>
+        <v>0.03353371186735126</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.03559169514490108</v>
+        <v>0.03183746506595035</v>
       </c>
       <c r="B84" t="n">
-        <v>0.03893298815209079</v>
+        <v>0.02445122571742906</v>
       </c>
       <c r="C84" t="n">
-        <v>0.08073700765681918</v>
+        <v>0.1371350851632207</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3853661228066294</v>
+        <v>0.2951433491621711</v>
       </c>
       <c r="E84" t="n">
-        <v>0.3757012709261572</v>
+        <v>0.4237508508897421</v>
       </c>
       <c r="F84" t="n">
-        <v>0.04373662497181472</v>
+        <v>0.05396711443833933</v>
       </c>
       <c r="G84" t="n">
-        <v>0.03993429034159312</v>
+        <v>0.03371490956314747</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.03596222987812418</v>
+        <v>0.03219488947611043</v>
       </c>
       <c r="B85" t="n">
-        <v>0.03927095405329993</v>
+        <v>0.0247021799062112</v>
       </c>
       <c r="C85" t="n">
-        <v>0.08126636189598879</v>
+        <v>0.1384850596807962</v>
       </c>
       <c r="D85" t="n">
-        <v>0.384050683923133</v>
+        <v>0.2935726459916718</v>
       </c>
       <c r="E85" t="n">
-        <v>0.3750993423683959</v>
+        <v>0.4226990903400529</v>
       </c>
       <c r="F85" t="n">
-        <v>0.04408360143855721</v>
+        <v>0.05445689524171882</v>
       </c>
       <c r="G85" t="n">
-        <v>0.04026682644250119</v>
+        <v>0.03388923936343845</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>0.03632271549803582</v>
+        <v>0.03254857200124536</v>
       </c>
       <c r="B86" t="n">
-        <v>0.03960307818179162</v>
+        <v>0.02495257226992437</v>
       </c>
       <c r="C86" t="n">
-        <v>0.08177759824102922</v>
+        <v>0.1398069588550175</v>
       </c>
       <c r="D86" t="n">
-        <v>0.3827784461397658</v>
+        <v>0.2922350547744933</v>
       </c>
       <c r="E86" t="n">
-        <v>0.3745020751788597</v>
+        <v>0.4214614103802705</v>
       </c>
       <c r="F86" t="n">
-        <v>0.04442328751183534</v>
+        <v>0.05493884799156151</v>
       </c>
       <c r="G86" t="n">
-        <v>0.04059279924867244</v>
+        <v>0.03405658372748732</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>0.03667318896325162</v>
+        <v>0.03289872538170997</v>
       </c>
       <c r="B87" t="n">
-        <v>0.03992935912060965</v>
+        <v>0.02520184199941011</v>
       </c>
       <c r="C87" t="n">
-        <v>0.08227037060001353</v>
+        <v>0.1411013232515507</v>
       </c>
       <c r="D87" t="n">
-        <v>0.3815427051851366</v>
+        <v>0.2911167645047252</v>
       </c>
       <c r="E87" t="n">
-        <v>0.3739167954363365</v>
+        <v>0.420050128612158</v>
       </c>
       <c r="F87" t="n">
-        <v>0.04475611304394684</v>
+        <v>0.0554143611043525</v>
       </c>
       <c r="G87" t="n">
-        <v>0.04091146765070141</v>
+        <v>0.03421685514609358</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.03701373387425092</v>
+        <v>0.03324559037769308</v>
       </c>
       <c r="B88" t="n">
-        <v>0.04024973510095686</v>
+        <v>0.02544956012876436</v>
       </c>
       <c r="C88" t="n">
-        <v>0.08274445731326178</v>
+        <v>0.1423687125060382</v>
       </c>
       <c r="D88" t="n">
-        <v>0.3803390604758969</v>
+        <v>0.2902001605720371</v>
       </c>
       <c r="E88" t="n">
-        <v>0.3733483195114755</v>
+        <v>0.4184812315185055</v>
       </c>
       <c r="F88" t="n">
-        <v>0.04508249528772774</v>
+        <v>0.05588474776742532</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0412221984364328</v>
+        <v>0.03436999712953669</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.03734446949617701</v>
+        <v>0.03358940721940507</v>
       </c>
       <c r="B89" t="n">
-        <v>0.04056408900233455</v>
+        <v>0.02569542168118489</v>
       </c>
       <c r="C89" t="n">
-        <v>0.08319974833303412</v>
+        <v>0.1436096542527374</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3791677427575967</v>
+        <v>0.2894661821207362</v>
       </c>
       <c r="E89" t="n">
-        <v>0.3727966590711655</v>
+        <v>0.4167721333804736</v>
       </c>
       <c r="F89" t="n">
-        <v>0.04540281715825882</v>
+        <v>0.05635121793988343</v>
       </c>
       <c r="G89" t="n">
-        <v>0.04152447418143766</v>
+        <v>0.03451598340557974</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>0.03766554136539462</v>
+        <v>0.03393039276334507</v>
       </c>
       <c r="B90" t="n">
-        <v>0.04087225352946373</v>
+        <v>0.02593923445251286</v>
       </c>
       <c r="C90" t="n">
-        <v>0.08363622056946719</v>
+        <v>0.1448245978646502</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3780345521697597</v>
+        <v>0.2888962111213901</v>
       </c>
       <c r="E90" t="n">
-        <v>0.3722561273058727</v>
+        <v>0.4149398930640288</v>
       </c>
       <c r="F90" t="n">
-        <v>0.04571740843083025</v>
+        <v>0.05681485479568295</v>
       </c>
       <c r="G90" t="n">
-        <v>0.04181789662920687</v>
+        <v>0.03465481593839054</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.03797711381327089</v>
+        <v>0.03426872450234526</v>
       </c>
       <c r="B91" t="n">
-        <v>0.04117401634761808</v>
+        <v>0.02618090602569024</v>
       </c>
       <c r="C91" t="n">
-        <v>0.08405390758831521</v>
+        <v>0.146013875752566</v>
       </c>
       <c r="D91" t="n">
-        <v>0.3769501244373961</v>
+        <v>0.2884732692082789</v>
       </c>
       <c r="E91" t="n">
-        <v>0.3717161193721643</v>
+        <v>0.4130001057170841</v>
       </c>
       <c r="F91" t="n">
-        <v>0.04602653196910855</v>
+        <v>0.05727659595804657</v>
       </c>
       <c r="G91" t="n">
-        <v>0.04210218647213522</v>
+        <v>0.03478652283598902</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.03827936395506088</v>
+        <v>0.03460453165942015</v>
       </c>
       <c r="B92" t="n">
-        <v>0.04146912531409753</v>
+        <v>0.02642042988916275</v>
       </c>
       <c r="C92" t="n">
-        <v>0.08445287112190362</v>
+        <v>0.147177674880513</v>
       </c>
       <c r="D92" t="n">
-        <v>0.3759279196584692</v>
+        <v>0.2881825258074662</v>
       </c>
       <c r="E92" t="n">
-        <v>0.3711631642837527</v>
+        <v>0.4109664606288098</v>
       </c>
       <c r="F92" t="n">
-        <v>0.04633037588183519</v>
+        <v>0.05773721999694319</v>
       </c>
       <c r="G92" t="n">
-        <v>0.04237717978488143</v>
+        <v>0.03491115713768527</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>0.03857247663315665</v>
+        <v>0.03493789242061674</v>
       </c>
       <c r="B93" t="n">
-        <v>0.04175729405977526</v>
+        <v>0.02665787082858772</v>
       </c>
       <c r="C93" t="n">
-        <v>0.08483318013632335</v>
+        <v>0.1483160216123814</v>
       </c>
       <c r="D93" t="n">
-        <v>0.3749817050598613</v>
+        <v>0.2880112768480893</v>
       </c>
       <c r="E93" t="n">
-        <v>0.3705834710166885</v>
+        <v>0.4088508028750958</v>
       </c>
       <c r="F93" t="n">
-        <v>0.04662905180362451</v>
+        <v>0.05819733862782779</v>
       </c>
       <c r="G93" t="n">
-        <v>0.04264282129057691</v>
+        <v>0.03502879678740135</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>0.03885664039706489</v>
+        <v>0.03526883597366209</v>
       </c>
       <c r="B94" t="n">
-        <v>0.04203820812582248</v>
+        <v>0.02689334952283627</v>
       </c>
       <c r="C94" t="n">
-        <v>0.08519489905257312</v>
+        <v>0.14942878115289</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3741232105602207</v>
+        <v>0.2879485723537816</v>
       </c>
       <c r="E94" t="n">
-        <v>0.3699652877670983</v>
+        <v>0.4066635203418885</v>
       </c>
       <c r="F94" t="n">
-        <v>0.04692259894321294</v>
+        <v>0.05865739489624465</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0428991551540045</v>
+        <v>0.03513954575869686</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.0391320447534538</v>
+        <v>0.03559734787607239</v>
       </c>
       <c r="B95" t="n">
-        <v>0.04231153172962369</v>
+        <v>0.02712702616314175</v>
       </c>
       <c r="C95" t="n">
-        <v>0.08553808278761632</v>
+        <v>0.15051567062065</v>
       </c>
       <c r="D95" t="n">
-        <v>0.3733603693225758</v>
+        <v>0.2879846494590141</v>
       </c>
       <c r="E95" t="n">
-        <v>0.3693006639227612</v>
+        <v>0.404414101905098</v>
       </c>
       <c r="F95" t="n">
-        <v>0.04721099303382403</v>
+        <v>0.05911766789486967</v>
       </c>
       <c r="G95" t="n">
-        <v>0.04314631445015342</v>
+        <v>0.03524353608115399</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.03939887856381659</v>
+        <v>0.03592337737483944</v>
       </c>
       <c r="B96" t="n">
-        <v>0.04257691496994433</v>
+        <v>0.02735908310179233</v>
       </c>
       <c r="C96" t="n">
-        <v>0.08586277564514533</v>
+        <v>0.1515762816583679</v>
       </c>
       <c r="D96" t="n">
-        <v>0.3726963165892779</v>
+        <v>0.2881103158202073</v>
       </c>
       <c r="E96" t="n">
-        <v>0.3685864447681664</v>
+        <v>0.4021117269649649</v>
       </c>
       <c r="F96" t="n">
-        <v>0.04749415897476748</v>
+        <v>0.05957828451065478</v>
       </c>
       <c r="G96" t="n">
-        <v>0.04338451048888164</v>
+        <v>0.03534093056917301</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0.03965732917110423</v>
+        <v>0.03624684515072457</v>
       </c>
       <c r="B97" t="n">
-        <v>0.04283400111007509</v>
+        <v>0.0275897066910042</v>
       </c>
       <c r="C97" t="n">
-        <v>0.08616901348448566</v>
+        <v>0.152610107595359</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3721291283369047</v>
+        <v>0.2883164013773541</v>
       </c>
       <c r="E97" t="n">
-        <v>0.3678245194619953</v>
+        <v>0.3997657751358525</v>
       </c>
       <c r="F97" t="n">
-        <v>0.04777198571626193</v>
+        <v>0.06003923825904078</v>
       </c>
       <c r="G97" t="n">
-        <v>0.04361402271916656</v>
+        <v>0.03543192579066488</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>0.03990758180980282</v>
+        <v>0.03656765044116904</v>
       </c>
       <c r="B98" t="n">
-        <v>0.04308243378464029</v>
+        <v>0.02781906896760322</v>
       </c>
       <c r="C98" t="n">
-        <v>0.08645683053021894</v>
+        <v>0.1536165709230879</v>
       </c>
       <c r="D98" t="n">
-        <v>0.3716521575951079</v>
+        <v>0.2885933448368299</v>
       </c>
       <c r="E98" t="n">
-        <v>0.3670214652302248</v>
+        <v>0.3973861951522451</v>
       </c>
       <c r="F98" t="n">
-        <v>0.04804434186059742</v>
+        <v>0.06050041467437203</v>
       </c>
       <c r="G98" t="n">
-        <v>0.04383518918940889</v>
+        <v>0.03551675500469297</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.04014981905629594</v>
+        <v>0.03688567641941976</v>
       </c>
       <c r="B99" t="n">
-        <v>0.0433218642177042</v>
+        <v>0.02804730999461339</v>
       </c>
       <c r="C99" t="n">
-        <v>0.08672627160308974</v>
+        <v>0.1545950502868051</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3712548050028996</v>
+        <v>0.2889309284711056</v>
       </c>
       <c r="E99" t="n">
-        <v>0.3661877525094467</v>
+        <v>0.394983722593703</v>
       </c>
       <c r="F99" t="n">
-        <v>0.04831109052508743</v>
+        <v>0.0609616217407031</v>
       </c>
       <c r="G99" t="n">
-        <v>0.04404839708547462</v>
+        <v>0.03559569049365015</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.04038422025443668</v>
+        <v>0.03720079329825413</v>
       </c>
       <c r="B100" t="n">
-        <v>0.04355195856787888</v>
+        <v>0.02827452198986778</v>
       </c>
       <c r="C100" t="n">
-        <v>0.08697740834589195</v>
+        <v>0.1555449084258162</v>
       </c>
       <c r="D100" t="n">
-        <v>0.3709235916449082</v>
+        <v>0.2893181445242407</v>
       </c>
       <c r="E100" t="n">
-        <v>0.3653366459004059</v>
+        <v>0.3925699637275302</v>
       </c>
       <c r="F100" t="n">
-        <v>0.04857210227815661</v>
+        <v>0.0614226231245017</v>
       </c>
       <c r="G100" t="n">
-        <v>0.04425407300831694</v>
+        <v>0.03566904490978919</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.04061096099551632</v>
+        <v>0.03751285905385273</v>
       </c>
       <c r="B101" t="n">
-        <v>0.04377240536371672</v>
+        <v>0.02850073638423136</v>
       </c>
       <c r="C101" t="n">
-        <v>0.08721035667715685</v>
+        <v>0.15646552292173</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3706434186099946</v>
+        <v>0.2897431735637552</v>
       </c>
       <c r="E101" t="n">
-        <v>0.3644829200753719</v>
+        <v>0.3901573653824588</v>
       </c>
       <c r="F101" t="n">
-        <v>0.04882726533890564</v>
+        <v>0.06188317139521929</v>
       </c>
       <c r="G101" t="n">
-        <v>0.04445267293933518</v>
+        <v>0.03573717129875296</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0.04083021279801562</v>
+        <v>0.03782171803592153</v>
       </c>
       <c r="B102" t="n">
-        <v>0.04398292290669618</v>
+        <v>0.02872591483856083</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0874252929894053</v>
+        <v>0.1573563207379944</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3703988930671163</v>
+        <v>0.290193463633135</v>
       </c>
       <c r="E102" t="n">
-        <v>0.3636415136731199</v>
+        <v>0.387759083135313</v>
       </c>
       <c r="F102" t="n">
-        <v>0.04907649259580363</v>
+        <v>0.06234303802844576</v>
       </c>
       <c r="G102" t="n">
-        <v>0.04464467196984068</v>
+        <v>0.03580046159062959</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>0.0410421431159207</v>
+        <v>0.0381271982023199</v>
       </c>
       <c r="B103" t="n">
-        <v>0.04418326653531684</v>
+        <v>0.02894994502166863</v>
       </c>
       <c r="C103" t="n">
-        <v>0.08762246762589039</v>
+        <v>0.1582168147706551</v>
       </c>
       <c r="D103" t="n">
-        <v>0.3701755841267427</v>
+        <v>0.2906559050028924</v>
       </c>
       <c r="E103" t="n">
-        <v>0.362826259277995</v>
+        <v>0.3853887562377107</v>
       </c>
       <c r="F103" t="n">
-        <v>0.04931972532231085</v>
+        <v>0.06280203734838305</v>
       </c>
       <c r="G103" t="n">
-        <v>0.04483055399582214</v>
+        <v>0.03585934341637022</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>0.04124691578479123</v>
+        <v>0.03842910772434953</v>
       </c>
       <c r="B104" t="n">
-        <v>0.04437323565171643</v>
+        <v>0.02917264150986717</v>
       </c>
       <c r="C104" t="n">
-        <v>0.08780221503438841</v>
+        <v>0.1590466406391907</v>
       </c>
       <c r="D104" t="n">
-        <v>0.3699610546285385</v>
+        <v>0.2911170840708832</v>
       </c>
       <c r="E104" t="n">
-        <v>0.362048843459343</v>
+        <v>0.3830602089445754</v>
       </c>
       <c r="F104" t="n">
-        <v>0.04955693379539903</v>
+        <v>0.0632600419215332</v>
       </c>
       <c r="G104" t="n">
-        <v>0.04501080164581155</v>
+        <v>0.03591427518960137</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>0.04144469193952859</v>
+        <v>0.03872723196426964</v>
       </c>
       <c r="B105" t="n">
-        <v>0.04455268041304233</v>
+        <v>0.02939375181772805</v>
       </c>
       <c r="C105" t="n">
-        <v>0.08796496012609956</v>
+        <v>0.1598455910974218</v>
       </c>
       <c r="D105" t="n">
-        <v>0.369745532416182</v>
+        <v>0.2915635762766305</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3613181331390901</v>
+        <v>0.3807871213797743</v>
       </c>
       <c r="F105" t="n">
-        <v>0.04978811528702243</v>
+        <v>0.06371698795157196</v>
       </c>
       <c r="G105" t="n">
-        <v>0.04518588667903431</v>
+        <v>0.03596573951260363</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0.04163563130800725</v>
+        <v>0.03902133164128158</v>
       </c>
       <c r="B106" t="n">
-        <v>0.0447215079320137</v>
+        <v>0.02961296721554504</v>
       </c>
       <c r="C106" t="n">
-        <v>0.08811122031157911</v>
+        <v>0.1606136452455227</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3695221556362495</v>
+        <v>0.2919822096297778</v>
       </c>
       <c r="E106" t="n">
-        <v>0.3606399337196017</v>
+        <v>0.3785827406407503</v>
       </c>
       <c r="F106" t="n">
-        <v>0.05001329006340641</v>
+        <v>0.06417287042904843</v>
       </c>
       <c r="G106" t="n">
-        <v>0.04535626102913725</v>
+        <v>0.03601423519807412</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0.0418198936914877</v>
+        <v>0.03931114291457443</v>
       </c>
       <c r="B107" t="n">
-        <v>0.04487968770984353</v>
+        <v>0.02982993733917358</v>
       </c>
       <c r="C107" t="n">
-        <v>0.08824160282063627</v>
+        <v>0.1613509909850624</v>
       </c>
       <c r="D107" t="n">
-        <v>0.3692868169119095</v>
+        <v>0.2923602191230285</v>
       </c>
       <c r="E107" t="n">
-        <v>0.3600171540795005</v>
+        <v>0.376459712496424</v>
       </c>
       <c r="F107" t="n">
-        <v>0.05023249607562277</v>
+        <v>0.06462772893496592</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0455223487109996</v>
+        <v>0.03606026820677154</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.04199764041106276</v>
+        <v>0.0395963797428138</v>
       </c>
       <c r="B108" t="n">
-        <v>0.04502725599337715</v>
+        <v>0.03004428748179654</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0883567973152133</v>
+        <v>0.1620580392998701</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3690377001666076</v>
+        <v>0.2926852481395464</v>
       </c>
       <c r="E108" t="n">
-        <v>0.3594502842363096</v>
+        <v>0.3744300775453159</v>
       </c>
       <c r="F108" t="n">
-        <v>0.05044578303025449</v>
+        <v>0.06508162582807302</v>
       </c>
       <c r="G108" t="n">
-        <v>0.04568453884716919</v>
+        <v>0.03610434196258436</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>0.04216903548993609</v>
+        <v>0.03987673894150665</v>
       </c>
       <c r="B109" t="n">
-        <v>0.04516431878186731</v>
+        <v>0.03025563711350821</v>
       </c>
       <c r="C109" t="n">
-        <v>0.08845756426193557</v>
+        <v>0.1627354287852812</v>
       </c>
       <c r="D109" t="n">
-        <v>0.3687746428834009</v>
+        <v>0.2929452327055901</v>
       </c>
       <c r="E109" t="n">
-        <v>0.3589380520412671</v>
+        <v>0.3725053950961751</v>
       </c>
       <c r="F109" t="n">
-        <v>0.05065320648004418</v>
+        <v>0.06553461970190368</v>
       </c>
       <c r="G109" t="n">
-        <v>0.04584318006153881</v>
+        <v>0.03614694765603512</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>0.04233424639168588</v>
+        <v>0.04015190759816185</v>
       </c>
       <c r="B110" t="n">
-        <v>0.04529105321902813</v>
+        <v>0.03046361826747672</v>
       </c>
       <c r="C110" t="n">
-        <v>0.08854472001117177</v>
+        <v>0.1633840202368868</v>
       </c>
       <c r="D110" t="n">
-        <v>0.3684984620304557</v>
+        <v>0.2931282858462003</v>
       </c>
       <c r="E110" t="n">
-        <v>0.3584781194219185</v>
+        <v>0.3706968766919748</v>
       </c>
       <c r="F110" t="n">
-        <v>0.05085482249207812</v>
+        <v>0.06598673644733608</v>
       </c>
       <c r="G110" t="n">
-        <v>0.04599857643366705</v>
+        <v>0.03618855491196339</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0.04249344420292708</v>
+        <v>0.0404215728768892</v>
       </c>
       <c r="B111" t="n">
-        <v>0.04540770719197337</v>
+        <v>0.03066789238785638</v>
       </c>
       <c r="C111" t="n">
-        <v>0.08861911974463561</v>
+        <v>0.1640048813624821</v>
       </c>
       <c r="D111" t="n">
-        <v>0.368210355773804</v>
+        <v>0.2932227191115956</v>
       </c>
       <c r="E111" t="n">
-        <v>0.358067704574238</v>
+        <v>0.3690153897517123</v>
       </c>
       <c r="F111" t="n">
-        <v>0.05105068333980046</v>
+        <v>0.06643794128639278</v>
       </c>
       <c r="G111" t="n">
-        <v>0.04615098517263189</v>
+        <v>0.03622960322307147</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>0.04264680325049842</v>
+        <v>0.04068543351180203</v>
       </c>
       <c r="B112" t="n">
-        <v>0.04551459707762263</v>
+        <v>0.0308681646689356</v>
       </c>
       <c r="C112" t="n">
-        <v>0.08868163954020369</v>
+        <v>0.1645992638966257</v>
       </c>
       <c r="D112" t="n">
-        <v>0.36791145253267</v>
+        <v>0.293217287792764</v>
       </c>
       <c r="E112" t="n">
-        <v>0.3577040569975783</v>
+        <v>0.3674712418666304</v>
       </c>
       <c r="F112" t="n">
-        <v>0.05124083451852297</v>
+        <v>0.06688811386254834</v>
       </c>
       <c r="G112" t="n">
-        <v>0.04630061608290263</v>
+        <v>0.03627049440069391</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0.04279450025473867</v>
+        <v>0.04094321248523167</v>
       </c>
       <c r="B113" t="n">
-        <v>0.04561210368360202</v>
+        <v>0.03106419505523736</v>
       </c>
       <c r="C113" t="n">
-        <v>0.08873315881300312</v>
+        <v>0.1651685749069208</v>
       </c>
       <c r="D113" t="n">
-        <v>0.3676025399869197</v>
+        <v>0.2931016647951827</v>
       </c>
       <c r="E113" t="n">
-        <v>0.3573847513333661</v>
+        <v>0.3660737378655793</v>
       </c>
       <c r="F113" t="n">
-        <v>0.05142531319805369</v>
+        <v>0.06733702863392228</v>
       </c>
       <c r="G113" t="n">
-        <v>0.04644763273032158</v>
+        <v>0.03631158625792594</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>0.04293671317445759</v>
+        <v>0.04119467023369396</v>
       </c>
       <c r="B114" t="n">
-        <v>0.04570066652953643</v>
+        <v>0.0312558053921845</v>
       </c>
       <c r="C114" t="n">
-        <v>0.08877454434444265</v>
+        <v>0.1657143452126351</v>
       </c>
       <c r="D114" t="n">
-        <v>0.3672839757606265</v>
+        <v>0.2928670852339288</v>
       </c>
       <c r="E114" t="n">
-        <v>0.3571077970478621</v>
+        <v>0.3648305640394827</v>
       </c>
       <c r="F114" t="n">
-        <v>0.05160414805501221</v>
+        <v>0.06778434213171132</v>
       </c>
       <c r="G114" t="n">
-        <v>0.04659215508806358</v>
+        <v>0.03635318775636363</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>0.0430736199303445</v>
+        <v>0.04143961767665856</v>
       </c>
       <c r="B115" t="n">
-        <v>0.0457807766239747</v>
+        <v>0.03144288250884624</v>
       </c>
       <c r="C115" t="n">
-        <v>0.08880663698925784</v>
+        <v>0.1662381957857686</v>
       </c>
       <c r="D115" t="n">
-        <v>0.3669557595057493</v>
+        <v>0.2925070726698095</v>
       </c>
       <c r="E115" t="n">
-        <v>0.356871583322822</v>
+        <v>0.3637470875403312</v>
       </c>
       <c r="F115" t="n">
-        <v>0.05177736028644208</v>
+        <v>0.06822958810939117</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0467342633414211</v>
+        <v>0.03639555570919523</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0.043205397158352</v>
+        <v>0.04167792816052734</v>
       </c>
       <c r="B116" t="n">
-        <v>0.0458529679434126</v>
+        <v>0.03162537733577161</v>
       </c>
       <c r="C116" t="n">
-        <v>0.08883024183125174</v>
+        <v>0.1667418029461604</v>
       </c>
       <c r="D116" t="n">
-        <v>0.3666177311475463</v>
+        <v>0.2920181571440083</v>
       </c>
       <c r="E116" t="n">
-        <v>0.3566746938822084</v>
+        <v>0.3628256606440004</v>
       </c>
       <c r="F116" t="n">
-        <v>0.05194496551078876</v>
+        <v>0.06867218069069708</v>
       </c>
       <c r="G116" t="n">
-        <v>0.04687400252644183</v>
+        <v>0.0364388930788353</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>0.04333221911467344</v>
+        <v>0.04190954780839343</v>
       </c>
       <c r="B117" t="n">
-        <v>0.04591780785202366</v>
+        <v>0.03180330027378929</v>
       </c>
       <c r="C117" t="n">
-        <v>0.088846122073807</v>
+        <v>0.1672268620391679</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3662698513377474</v>
+        <v>0.2914005066015246</v>
       </c>
       <c r="E117" t="n">
-        <v>0.3565156357419042</v>
+        <v>0.3620650088551589</v>
       </c>
       <c r="F117" t="n">
-        <v>0.05210697620932363</v>
+        <v>0.06911142569559425</v>
       </c>
       <c r="G117" t="n">
-        <v>0.04701138767052574</v>
+        <v>0.03648334872637159</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0.04345425680096356</v>
+        <v>0.04213450336484063</v>
       </c>
       <c r="B118" t="n">
-        <v>0.04597588678907374</v>
+        <v>0.03197671348720562</v>
       </c>
       <c r="C118" t="n">
-        <v>0.08885499641335004</v>
+        <v>0.1676950499429198</v>
       </c>
       <c r="D118" t="n">
-        <v>0.3659125159361634</v>
+        <v>0.2906584103522185</v>
       </c>
       <c r="E118" t="n">
-        <v>0.35639253055545</v>
+        <v>0.3614597653735911</v>
       </c>
       <c r="F118" t="n">
-        <v>0.05226340437058549</v>
+        <v>0.06954653901063135</v>
       </c>
       <c r="G118" t="n">
-        <v>0.04714640913440686</v>
+        <v>0.03652901846859269</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0.04357167732126456</v>
+        <v>0.04235290722740146</v>
       </c>
       <c r="B119" t="n">
-        <v>0.04602780765246719</v>
+        <v>0.03214572073017789</v>
       </c>
       <c r="C119" t="n">
-        <v>0.08885753925468884</v>
+        <v>0.1681479864246552</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3655468554411859</v>
+        <v>0.2898005659678191</v>
       </c>
       <c r="E119" t="n">
-        <v>0.3563028184018672</v>
+        <v>0.3610002013538386</v>
       </c>
       <c r="F119" t="n">
-        <v>0.05241426403149465</v>
+        <v>0.06997667117722271</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0472790378970348</v>
+        <v>0.036575947118885</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>0.04368464351189497</v>
+        <v>0.0425649592709549</v>
       </c>
       <c r="B120" t="n">
-        <v>0.04607417533826718</v>
+        <v>0.03231045566463688</v>
       </c>
       <c r="C120" t="n">
-        <v>0.08885438286194618</v>
+        <v>0.1685871958369674</v>
       </c>
       <c r="D120" t="n">
-        <v>0.3651749729894956</v>
+        <v>0.2888401319811837</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3562430212469734</v>
+        <v>0.3606721894369068</v>
       </c>
       <c r="F120" t="n">
-        <v>0.05255957350710097</v>
+        <v>0.07040093645643176</v>
       </c>
       <c r="G120" t="n">
-        <v>0.04740923054432196</v>
+        <v>0.03662413135291864</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>0.04379331381047179</v>
+        <v>0.04277094538025671</v>
       </c>
       <c r="B121" t="n">
-        <v>0.0461155868888788</v>
+        <v>0.03247106943478094</v>
       </c>
       <c r="C121" t="n">
-        <v>0.08884612046808466</v>
+        <v>0.1690140707191755</v>
       </c>
       <c r="D121" t="n">
-        <v>0.3648000831119985</v>
+        <v>0.2877945212534751</v>
       </c>
       <c r="E121" t="n">
-        <v>0.3562086048953363</v>
+        <v>0.3604574255425121</v>
       </c>
       <c r="F121" t="n">
-        <v>0.05269935709280306</v>
+        <v>0.07081844457740138</v>
       </c>
       <c r="G121" t="n">
-        <v>0.04753693373243049</v>
+        <v>0.03667352309239811</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0.04389784242382141</v>
+        <v>0.04297123287572973</v>
       </c>
       <c r="B122" t="n">
-        <v>0.04615262274484423</v>
+        <v>0.03262771841987655</v>
       </c>
       <c r="C122" t="n">
-        <v>0.08883330954150719</v>
+        <v>0.1694298387571739</v>
       </c>
       <c r="D122" t="n">
-        <v>0.3644265258848095</v>
+        <v>0.2866849292739635</v>
       </c>
       <c r="E122" t="n">
-        <v>0.3561939651894196</v>
+        <v>0.3603339140890545</v>
       </c>
       <c r="F122" t="n">
-        <v>0.05283364618573321</v>
+        <v>0.07122833325221452</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0476620880298723</v>
+        <v>0.03672403333198677</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>0.04399837977087404</v>
+        <v>0.0431662631710235</v>
       </c>
       <c r="B123" t="n">
-        <v>0.04618583941459073</v>
+        <v>0.03278055279979553</v>
       </c>
       <c r="C123" t="n">
-        <v>0.08881647445149549</v>
+        <v>0.1698355347385863</v>
       </c>
       <c r="D123" t="n">
-        <v>0.3640596499845589</v>
+        <v>0.2855356182407127</v>
       </c>
       <c r="E123" t="n">
-        <v>0.3561925456230456</v>
+        <v>0.3602766951652157</v>
       </c>
       <c r="F123" t="n">
-        <v>0.05296247972511162</v>
+        <v>0.07162979963422191</v>
       </c>
       <c r="G123" t="n">
-        <v>0.04778463103031927</v>
+        <v>0.03677553625044453</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>0.04409507317858082</v>
+        <v>0.04335654204703943</v>
       </c>
       <c r="B124" t="n">
-        <v>0.04621576378851054</v>
+        <v>0.03292970656242077</v>
       </c>
       <c r="C124" t="n">
-        <v>0.08879610814074636</v>
+        <v>0.1702319784878265</v>
       </c>
       <c r="D124" t="n">
-        <v>0.363705574626499</v>
+        <v>0.2843730083407545</v>
       </c>
       <c r="E124" t="n">
-        <v>0.3561970765520174</v>
+        <v>0.3602587620717856</v>
       </c>
       <c r="F124" t="n">
-        <v>0.05308590394960463</v>
+        <v>0.07202212888285277</v>
       </c>
       <c r="G124" t="n">
-        <v>0.04790449976404043</v>
+        <v>0.0368278736073203</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>0.04418806783752702</v>
+        <v>0.04354262811479952</v>
       </c>
       <c r="B125" t="n">
-        <v>0.04624288918516199</v>
+        <v>0.03307528937498005</v>
       </c>
       <c r="C125" t="n">
-        <v>0.08877267262849974</v>
+        <v>0.1706197595263854</v>
       </c>
       <c r="D125" t="n">
-        <v>0.3633708556576353</v>
+        <v>0.2832246543011083</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3561999105594847</v>
+        <v>0.3602520907727313</v>
       </c>
       <c r="F125" t="n">
-        <v>0.05320397158534678</v>
+        <v>0.07240471847709276</v>
       </c>
       <c r="G125" t="n">
-        <v>0.04802163254634766</v>
+        <v>0.03688085943290239</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>0.04427750790373487</v>
+        <v>0.04372512003675585</v>
       </c>
       <c r="B126" t="n">
-        <v>0.0462676729457547</v>
+        <v>0.03321738061278261</v>
       </c>
       <c r="C126" t="n">
-        <v>0.08874659846258517</v>
+        <v>0.1709992287045504</v>
       </c>
       <c r="D126" t="n">
-        <v>0.3630620936921776</v>
+        <v>0.282118198773933</v>
       </c>
       <c r="E126" t="n">
-        <v>0.3561934161232613</v>
+        <v>0.3602286893771123</v>
       </c>
       <c r="F126" t="n">
-        <v>0.05331674052565463</v>
+        <v>0.0727770974181403</v>
       </c>
       <c r="G126" t="n">
-        <v>0.04813597034683607</v>
+        <v>0.03693428507672527</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>0.04436353770099965</v>
+        <v>0.04390464287853101</v>
       </c>
       <c r="B127" t="n">
-        <v>0.04629053532941413</v>
+        <v>0.03335602566081936</v>
       </c>
       <c r="C127" t="n">
-        <v>0.08871828343881877</v>
+        <v>0.1713704972489342</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3627855276459642</v>
+        <v>0.2810803892428623</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3561703858306099</v>
+        <v>0.3601615807971925</v>
       </c>
       <c r="F127" t="n">
-        <v>0.05342427220988509</v>
+        <v>0.07313893955292469</v>
       </c>
       <c r="G127" t="n">
-        <v>0.04824745784430243</v>
+        <v>0.03698792461873555</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>0.04444630292232495</v>
+        <v>0.04408183412876949</v>
       </c>
       <c r="B128" t="n">
-        <v>0.04631185935950671</v>
+        <v>0.03349123456986768</v>
       </c>
       <c r="C128" t="n">
-        <v>0.08868809113230916</v>
+        <v>0.1717334435555022</v>
       </c>
       <c r="D128" t="n">
-        <v>0.3625466560524273</v>
+        <v>0.2801362199635601</v>
       </c>
       <c r="E128" t="n">
-        <v>0.3561244163038418</v>
+        <v>0.3600256559256719</v>
       </c>
       <c r="F128" t="n">
-        <v>0.05352662992238843</v>
+        <v>0.07349007110014737</v>
       </c>
       <c r="G128" t="n">
-        <v>0.04835604430721079</v>
+        <v>0.03704154075648133</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0.04452595172677037</v>
+        <v>0.04425732965257084</v>
       </c>
       <c r="B129" t="n">
-        <v>0.04633199121527971</v>
+        <v>0.03362298295311767</v>
       </c>
       <c r="C129" t="n">
-        <v>0.08865634965825019</v>
+        <v>0.1720877273467018</v>
       </c>
       <c r="D129" t="n">
-        <v>0.3623499213298452</v>
+        <v>0.2793082240038868</v>
       </c>
       <c r="E129" t="n">
-        <v>0.3560502243734082</v>
+        <v>0.3597983723770738</v>
       </c>
       <c r="F129" t="n">
-        <v>0.05362387731824094</v>
+        <v>0.0738304725440013</v>
       </c>
       <c r="G129" t="n">
-        <v>0.04846168437820269</v>
+        <v>0.03709489112264752</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>0.0446026356119552</v>
+        <v>0.04443174990286341</v>
       </c>
       <c r="B130" t="n">
-        <v>0.04635124088079878</v>
+        <v>0.03375121497180254</v>
       </c>
       <c r="C130" t="n">
-        <v>0.08862335106561491</v>
+        <v>0.1724328108535649</v>
       </c>
       <c r="D130" t="n">
-        <v>0.362198482011318</v>
+        <v>0.2786159028506683</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3559438741493223</v>
+        <v>0.3594603109051304</v>
       </c>
       <c r="F130" t="n">
-        <v>0.05371607743384914</v>
+        <v>0.07416027544142346</v>
       </c>
       <c r="G130" t="n">
-        <v>0.04856433884715286</v>
+        <v>0.03714773507454697</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0.04467650988305696</v>
+        <v>0.04460568666684733</v>
       </c>
       <c r="B131" t="n">
-        <v>0.04636988273104102</v>
+        <v>0.033875848084631</v>
       </c>
       <c r="C131" t="n">
-        <v>0.08858935165472065</v>
+        <v>0.1727679864842602</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3620940858635928</v>
+        <v>0.2780752578697636</v>
       </c>
       <c r="E131" t="n">
-        <v>0.355802902157446</v>
+        <v>0.3589956252755813</v>
       </c>
       <c r="F131" t="n">
-        <v>0.05380329236109986</v>
+        <v>0.07447975486602375</v>
       </c>
       <c r="G131" t="n">
-        <v>0.04866397534905072</v>
+        <v>0.03719984075289326</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0.04474773370894577</v>
+        <v>0.04477969062592004</v>
       </c>
       <c r="B132" t="n">
-        <v>0.04638815600540624</v>
+        <v>0.033996779220806</v>
       </c>
       <c r="C132" t="n">
-        <v>0.08855457319294634</v>
+        <v>0.1730924095129215</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3620370429742057</v>
+        <v>0.277698386194652</v>
       </c>
       <c r="E132" t="n">
-        <v>0.3556263411990265</v>
+        <v>0.358392423986533</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0538855838516429</v>
+        <v>0.0747893182514795</v>
       </c>
       <c r="G132" t="n">
-        <v>0.04876056906782535</v>
+        <v>0.03725099220768791</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>0.04481646965007916</v>
+        <v>0.04495425997489979</v>
       </c>
       <c r="B133" t="n">
-        <v>0.04640626506547185</v>
+        <v>0.03411389195107037</v>
       </c>
       <c r="C133" t="n">
-        <v>0.08851920506786669</v>
+        <v>0.1734051347873753</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3620262903678481</v>
+        <v>0.2774931226357646</v>
       </c>
       <c r="E133" t="n">
-        <v>0.3554146517252368</v>
+        <v>0.3576431029980501</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0539630147941462</v>
+        <v>0.07508949140081979</v>
       </c>
       <c r="G133" t="n">
-        <v>0.04885410332935593</v>
+        <v>0.03730099625201991</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>0.04488288272572585</v>
+        <v>0.04512983040038276</v>
       </c>
       <c r="B134" t="n">
-        <v>0.04642437954382679</v>
+        <v>0.03422706413149603</v>
       </c>
       <c r="C134" t="n">
-        <v>0.08848340712208047</v>
+        <v>0.1737051558300935</v>
       </c>
       <c r="D134" t="n">
-        <v>0.362059529747709</v>
+        <v>0.277462740699737</v>
       </c>
       <c r="E134" t="n">
-        <v>0.3551695791835353</v>
+        <v>0.3567446177648389</v>
       </c>
       <c r="F134" t="n">
-        <v>0.05403565156230271</v>
+        <v>0.07538090259027644</v>
       </c>
       <c r="G134" t="n">
-        <v>0.04894457011482698</v>
+        <v>0.03734968858317543</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>0.04494713905243405</v>
+        <v>0.04530676664969721</v>
       </c>
       <c r="B135" t="n">
-        <v>0.0464426344858619</v>
+        <v>0.03433617559200086</v>
       </c>
       <c r="C135" t="n">
-        <v>0.08844731296434613</v>
+        <v>0.1739914447560551</v>
       </c>
       <c r="D135" t="n">
-        <v>0.3621334171428796</v>
+        <v>0.27760575278421</v>
       </c>
       <c r="E135" t="n">
-        <v>0.3548939589088581</v>
+        <v>0.3556986558452478</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0541035669953409</v>
+        <v>0.07566426559314612</v>
       </c>
       <c r="G135" t="n">
-        <v>0.04903197045028275</v>
+        <v>0.03739693877964317</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>0.04500940415717242</v>
+        <v>0.04548535592180371</v>
       </c>
       <c r="B136" t="n">
-        <v>0.0464611306258547</v>
+        <v>0.03444111545360512</v>
       </c>
       <c r="C136" t="n">
-        <v>0.08841103353532141</v>
+        <v>0.1742629913901415</v>
       </c>
       <c r="D136" t="n">
-        <v>0.3622437810894433</v>
+        <v>0.2779158587366659</v>
       </c>
       <c r="E136" t="n">
-        <v>0.3545914921888235</v>
+        <v>0.3545116622134276</v>
       </c>
       <c r="F136" t="n">
-        <v>0.05416684374591552</v>
+        <v>0.07594036240990652</v>
       </c>
       <c r="G136" t="n">
-        <v>0.04911631465747715</v>
+        <v>0.03744265387444949</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>0.04506984108355728</v>
+        <v>0.04566580321805774</v>
       </c>
       <c r="B137" t="n">
-        <v>0.04647993500251345</v>
+        <v>0.03454178873975675</v>
       </c>
       <c r="C137" t="n">
-        <v>0.08837466072842053</v>
+        <v>0.1745188404029181</v>
       </c>
       <c r="D137" t="n">
-        <v>0.3623858476507962</v>
+        <v>0.2783820803108101</v>
       </c>
       <c r="E137" t="n">
-        <v>0.354266515382313</v>
+        <v>0.3531946808024057</v>
       </c>
       <c r="F137" t="n">
-        <v>0.05422557765219937</v>
+        <v>0.07621002626614813</v>
       </c>
       <c r="G137" t="n">
-        <v>0.04919762250020021</v>
+        <v>0.03748678025990372</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>0.04512860840104302</v>
+        <v>0.04584822879143523</v>
       </c>
       <c r="B138" t="n">
-        <v>0.04649908201511058</v>
+        <v>0.03463812212660407</v>
       </c>
       <c r="C138" t="n">
-        <v>0.08833827090971905</v>
+        <v>0.1747581249310902</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3625544549878427</v>
+        <v>0.2789890952260209</v>
       </c>
       <c r="E138" t="n">
-        <v>0.3539237797285755</v>
+        <v>0.3517629996898556</v>
       </c>
       <c r="F138" t="n">
-        <v>0.05427988079113936</v>
+        <v>0.07647412531705178</v>
       </c>
       <c r="G138" t="n">
-        <v>0.04927592316656588</v>
+        <v>0.03752930391794209</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0.04518585824060203</v>
+        <v>0.04603266760883693</v>
       </c>
       <c r="B139" t="n">
-        <v>0.04651857511770664</v>
+        <v>0.03473006873439487</v>
       </c>
       <c r="C139" t="n">
-        <v>0.08830192818870709</v>
+        <v>0.1749800959943641</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3627442446557755</v>
+        <v>0.2797177592824545</v>
       </c>
       <c r="E139" t="n">
-        <v>0.3535682547527277</v>
+        <v>0.3502356123796063</v>
       </c>
       <c r="F139" t="n">
-        <v>0.05432988389933818</v>
+        <v>0.07673354699557991</v>
       </c>
       <c r="G139" t="n">
-        <v>0.04935125514515144</v>
+        <v>0.03757024900476334</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>0.04524173448115124</v>
+        <v>0.04621907079040704</v>
       </c>
       <c r="B140" t="n">
-        <v>0.04653838916988414</v>
+        <v>0.03481761195360718</v>
       </c>
       <c r="C140" t="n">
-        <v>0.08826568732233382</v>
+        <v>0.1751841466181388</v>
       </c>
       <c r="D140" t="n">
-        <v>0.362949822873846</v>
+        <v>0.2805457873295621</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3532049622874116</v>
+        <v>0.3486345253213324</v>
       </c>
       <c r="F140" t="n">
-        <v>0.05437573792313975</v>
+        <v>0.07698918304253259</v>
       </c>
       <c r="G140" t="n">
-        <v>0.04942366594223663</v>
+        <v>0.03760967494441984</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0.04529637114840976</v>
+        <v>0.04640730886401112</v>
       </c>
       <c r="B141" t="n">
-        <v>0.04655847350812227</v>
+        <v>0.0349007683885446</v>
       </c>
       <c r="C141" t="n">
-        <v>0.08822959623596863</v>
+        <v>0.1753698300518647</v>
       </c>
       <c r="D141" t="n">
-        <v>0.3631658900003683</v>
+        <v>0.2814485536756695</v>
       </c>
       <c r="E141" t="n">
-        <v>0.3528388429152292</v>
+        <v>0.3469839518537609</v>
       </c>
       <c r="F141" t="n">
-        <v>0.05441761451103746</v>
+        <v>0.0772419149278787</v>
       </c>
       <c r="G141" t="n">
-        <v>0.04949321168085898</v>
+        <v>0.03764767223827054</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>0.04534989108111096</v>
+        <v>0.04659717666122265</v>
       </c>
       <c r="B142" t="n">
-        <v>0.04657875560429428</v>
+        <v>0.03497958996423698</v>
       </c>
       <c r="C142" t="n">
-        <v>0.08819369828774927</v>
+        <v>0.1755368713975169</v>
       </c>
       <c r="D142" t="n">
-        <v>0.3633873407722694</v>
+        <v>0.2823999693132894</v>
       </c>
       <c r="E142" t="n">
-        <v>0.352474652375589</v>
+        <v>0.3453094358708956</v>
       </c>
       <c r="F142" t="n">
-        <v>0.05445570534977446</v>
+        <v>0.07749259959379382</v>
       </c>
       <c r="G142" t="n">
-        <v>0.04955995652920868</v>
+        <v>0.03768435719904434</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0.04540240494499224</v>
+        <v>0.04678839962566218</v>
       </c>
       <c r="B143" t="n">
-        <v>0.0465991452552446</v>
+        <v>0.03505416524824348</v>
       </c>
       <c r="C143" t="n">
-        <v>0.08815803399755084</v>
+        <v>0.1756851724698605</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3636093395355982</v>
+        <v>0.283373393169501</v>
       </c>
       <c r="E143" t="n">
-        <v>0.352116883810721</v>
+        <v>0.343636948253551</v>
       </c>
       <c r="F143" t="n">
-        <v>0.05449022040297269</v>
+        <v>0.07774205533416456</v>
       </c>
       <c r="G143" t="n">
-        <v>0.04962397205291151</v>
+        <v>0.0377198658990169</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>0.04545401057657512</v>
+        <v>0.04698064148858376</v>
       </c>
       <c r="B144" t="n">
-        <v>0.04661953906876463</v>
+        <v>0.03512461995460853</v>
       </c>
       <c r="C144" t="n">
-        <v>0.08812264250868886</v>
+        <v>0.175814809470279</v>
       </c>
       <c r="D144" t="n">
-        <v>0.3638273765354226</v>
+        <v>0.2843425373183721</v>
       </c>
       <c r="E144" t="n">
-        <v>0.3517697097556238</v>
+        <v>0.3419919959984729</v>
       </c>
       <c r="F144" t="n">
-        <v>0.05452138510262378</v>
+        <v>0.07799104816125702</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0496853364523008</v>
+        <v>0.03775434760842658</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>0.04550479268536192</v>
+        <v>0.04717351304463769</v>
       </c>
       <c r="B145" t="n">
-        <v>0.04663982508867311</v>
+        <v>0.03519111657789779</v>
       </c>
       <c r="C145" t="n">
-        <v>0.08808756258035395</v>
+        <v>0.1759260242975417</v>
       </c>
       <c r="D145" t="n">
-        <v>0.3640373109190059</v>
+        <v>0.2852823291945602</v>
       </c>
       <c r="E145" t="n">
-        <v>0.351436938279555</v>
+        <v>0.3403987801184981</v>
       </c>
       <c r="F145" t="n">
-        <v>0.05454943669709625</v>
+        <v>0.07824027867118725</v>
       </c>
       <c r="G145" t="n">
-        <v>0.04974413374994831</v>
+        <v>0.03778795809567747</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>0.04555482290391955</v>
+        <v>0.0473665819677939</v>
       </c>
       <c r="B146" t="n">
-        <v>0.04665988733534587</v>
+        <v>0.03525385306335136</v>
       </c>
       <c r="C146" t="n">
-        <v>0.08805283320952625</v>
+        <v>0.1760192100636577</v>
       </c>
       <c r="D146" t="n">
-        <v>0.3642354048246787</v>
+        <v>0.2861696996709099</v>
       </c>
       <c r="E146" t="n">
-        <v>0.351121978831585</v>
+        <v>0.3388794322494689</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0545746199619023</v>
+        <v>0.07849036990326003</v>
       </c>
       <c r="G146" t="n">
-        <v>0.04980045293303751</v>
+        <v>0.03782085308155827</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>0.04560416013836578</v>
+        <v>0.04755938353997492</v>
       </c>
       <c r="B147" t="n">
-        <v>0.04667961007121423</v>
+        <v>0.0353130604142079</v>
       </c>
       <c r="C147" t="n">
-        <v>0.08801849400249658</v>
+        <v>0.1760948921220346</v>
       </c>
       <c r="D147" t="n">
-        <v>0.3644183520955481</v>
+        <v>0.286984270750214</v>
       </c>
       <c r="E147" t="n">
-        <v>0.3508278141218002</v>
+        <v>0.337453354355125</v>
       </c>
       <c r="F147" t="n">
-        <v>0.05459718251950608</v>
+        <v>0.07874185658022456</v>
       </c>
       <c r="G147" t="n">
-        <v>0.04985438705106795</v>
+        <v>0.03785318223821901</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>0.04565285122547473</v>
+        <v>0.04775143203479251</v>
       </c>
       <c r="B148" t="n">
-        <v>0.04669888166754452</v>
+        <v>0.03536899920150365</v>
       </c>
       <c r="C148" t="n">
-        <v>0.08798458513820841</v>
+        <v>0.1761537061766628</v>
       </c>
       <c r="D148" t="n">
-        <v>0.3645833024574325</v>
+        <v>0.2877089216740088</v>
       </c>
       <c r="E148" t="n">
-        <v>0.3505569771061971</v>
+        <v>0.3361366808624424</v>
       </c>
       <c r="F148" t="n">
-        <v>0.05461737007490037</v>
+        <v>0.07899517601760363</v>
       </c>
       <c r="G148" t="n">
-        <v>0.04990603233025127</v>
+        <v>0.03788508403298601</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0.04570093181008954</v>
+        <v>0.04794223254029349</v>
       </c>
       <c r="B149" t="n">
-        <v>0.04671759790483068</v>
+        <v>0.03542195495581144</v>
       </c>
       <c r="C149" t="n">
-        <v>0.08795114726234853</v>
+        <v>0.1761963750303308</v>
       </c>
       <c r="D149" t="n">
-        <v>0.364727881217655</v>
+        <v>0.2883302172440732</v>
       </c>
       <c r="E149" t="n">
-        <v>0.350311532773544</v>
+        <v>0.3349418775275933</v>
       </c>
       <c r="F149" t="n">
-        <v>0.05463542177419775</v>
+        <v>0.07925066103998965</v>
       </c>
       <c r="G149" t="n">
-        <v>0.04995548725733277</v>
+        <v>0.03791668166190808</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>0.04574842742331611</v>
+        <v>0.04813129296328383</v>
       </c>
       <c r="B150" t="n">
-        <v>0.04673566467093498</v>
+        <v>0.03547223252037701</v>
       </c>
       <c r="C150" t="n">
-        <v>0.08791822118806955</v>
+        <v>0.1762236852095835</v>
       </c>
       <c r="D150" t="n">
-        <v>0.3648502028818485</v>
+        <v>0.2888386852561202</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3500930661903924</v>
+        <v>0.3338774885209442</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0546515659612535</v>
+        <v>0.07950853527299372</v>
       </c>
       <c r="G150" t="n">
-        <v>0.05000285168417778</v>
+        <v>0.03794808025669746</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>0.04579535469783787</v>
+        <v>0.04831813583497566</v>
       </c>
       <c r="B151" t="n">
-        <v>0.04675300000756486</v>
+        <v>0.03552014957034675</v>
       </c>
       <c r="C151" t="n">
-        <v>0.08788584757144957</v>
+        <v>0.1762364650364446</v>
       </c>
       <c r="D151" t="n">
-        <v>0.3649488766793036</v>
+        <v>0.2892289336066458</v>
       </c>
       <c r="E151" t="n">
-        <v>0.3499026785953178</v>
+        <v>0.3329480395989657</v>
       </c>
       <c r="F151" t="n">
-        <v>0.05466601650682668</v>
+        <v>0.07976891090234174</v>
       </c>
       <c r="G151" t="n">
-        <v>0.05004822594169644</v>
+        <v>0.03797936545027974</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0.04584172266581003</v>
+        <v>0.04850230952641336</v>
       </c>
       <c r="B152" t="n">
-        <v>0.0467695355070544</v>
+        <v>0.03556602947523499</v>
       </c>
       <c r="C152" t="n">
-        <v>0.08785406656265114</v>
+        <v>0.1762355648618776</v>
       </c>
       <c r="D152" t="n">
-        <v>0.3650230017886437</v>
+        <v>0.2894996023559221</v>
       </c>
       <c r="E152" t="n">
-        <v>0.3497409936512456</v>
+        <v>0.33215410141928</v>
       </c>
       <c r="F152" t="n">
-        <v>0.05467896986026623</v>
+        <v>0.08003178911247978</v>
       </c>
       <c r="G152" t="n">
-        <v>0.05009170996432843</v>
+        <v>0.038010603248792</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>0.04588753408799034</v>
+        <v>0.04868339857840592</v>
       </c>
       <c r="B153" t="n">
-        <v>0.04678521710492081</v>
+        <v>0.03561019385590633</v>
       </c>
       <c r="C153" t="n">
-        <v>0.08782291752629411</v>
+        <v>0.1762218402572669</v>
       </c>
       <c r="D153" t="n">
-        <v>0.3650721505825399</v>
+        <v>0.2896531530700845</v>
       </c>
       <c r="E153" t="n">
-        <v>0.349608175342051</v>
+        <v>0.331492509782024</v>
       </c>
       <c r="F153" t="n">
-        <v>0.05469060291936465</v>
+        <v>0.08029706337026338</v>
       </c>
       <c r="G153" t="n">
-        <v>0.05013340243684018</v>
+        <v>0.03804184108604906</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>0.04593278675244923</v>
+        <v>0.04886103268883938</v>
       </c>
       <c r="B154" t="n">
-        <v>0.04680000530220143</v>
+        <v>0.03565295508951468</v>
       </c>
       <c r="C154" t="n">
-        <v>0.08779243884224869</v>
+        <v>0.1761961385941984</v>
       </c>
       <c r="D154" t="n">
-        <v>0.3650963387511711</v>
+        <v>0.289695506409354</v>
       </c>
       <c r="E154" t="n">
-        <v>0.3495039586495274</v>
+        <v>0.3309567319151314</v>
       </c>
       <c r="F154" t="n">
-        <v>0.05470107175151489</v>
+        <v>0.0805645254847817</v>
       </c>
       <c r="G154" t="n">
-        <v>0.05017339995089076</v>
+        <v>0.03807310981818038</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0.04597747470727869</v>
+        <v>0.04903489414588245</v>
       </c>
       <c r="B155" t="n">
-        <v>0.04681387490415337</v>
+        <v>0.03569460909678187</v>
       </c>
       <c r="C155" t="n">
-        <v>0.08776266769335589</v>
+        <v>0.1761592892241967</v>
       </c>
       <c r="D155" t="n">
-        <v>0.3650959826447107</v>
+        <v>0.2896355490399458</v>
       </c>
       <c r="E155" t="n">
-        <v>0.3494276926765926</v>
+        <v>0.3305373576088559</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0547105111776577</v>
+        <v>0.08083387450682326</v>
       </c>
       <c r="G155" t="n">
-        <v>0.05021179619626074</v>
+        <v>0.03810442637751367</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0.0460215893765512</v>
+        <v>0.04920472344679468</v>
       </c>
       <c r="B156" t="n">
-        <v>0.04682681435039551</v>
+        <v>0.035735428679796</v>
       </c>
       <c r="C156" t="n">
-        <v>0.08773363993296138</v>
+        <v>0.1761120973246227</v>
       </c>
       <c r="D156" t="n">
-        <v>0.3650718450580622</v>
+        <v>0.2894845400157318</v>
       </c>
       <c r="E156" t="n">
-        <v>0.3493783949181905</v>
+        <v>0.3302226855481059</v>
       </c>
       <c r="F156" t="n">
-        <v>0.05471903516694569</v>
+        <v>0.08110472821748389</v>
       </c>
       <c r="G156" t="n">
-        <v>0.05024868119689091</v>
+        <v>0.03813579676746504</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>0.04606512053133364</v>
+        <v>0.04937032293039306</v>
       </c>
       <c r="B157" t="n">
-        <v>0.04683882470747298</v>
+        <v>0.03577565764725675</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0877053899482137</v>
+        <v>0.1760553412895644</v>
       </c>
       <c r="D157" t="n">
-        <v>0.3650249721890784</v>
+        <v>0.2892554536474681</v>
       </c>
       <c r="E157" t="n">
-        <v>0.3493548140773045</v>
+        <v>0.3299993685482835</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0547267379440137</v>
+        <v>0.08137663684069173</v>
       </c>
       <c r="G157" t="n">
-        <v>0.05028414060258475</v>
+        <v>0.03816721909634267</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>0.04610805711246573</v>
+        <v>0.04953155840639494</v>
       </c>
       <c r="B158" t="n">
-        <v>0.04684991841673734</v>
+        <v>0.03581550591394286</v>
       </c>
       <c r="C158" t="n">
-        <v>0.08767795042272938</v>
+        <v>0.175989773277383</v>
       </c>
       <c r="D158" t="n">
-        <v>0.3649566257345438</v>
+        <v>0.2889622991526589</v>
       </c>
       <c r="E158" t="n">
-        <v>0.3493554975245522</v>
+        <v>0.3298530783465536</v>
       </c>
       <c r="F158" t="n">
-        <v>0.05473369571606176</v>
+        <v>0.08164909853367383</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0503182550729061</v>
+        <v>0.03819868636939246</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>0.04615038788101179</v>
+        <v>0.04968835875903298</v>
       </c>
       <c r="B159" t="n">
-        <v>0.04686011786245704</v>
+        <v>0.03585514572357629</v>
       </c>
       <c r="C159" t="n">
-        <v>0.08765135209888661</v>
+        <v>0.1759161224505431</v>
       </c>
       <c r="D159" t="n">
-        <v>0.3648682145378996</v>
+        <v>0.2886194566462103</v>
       </c>
       <c r="E159" t="n">
-        <v>0.3493788590083139</v>
+        <v>0.3297691516723171</v>
       </c>
       <c r="F159" t="n">
-        <v>0.05473996884222054</v>
+        <v>0.08192157591615508</v>
       </c>
       <c r="G159" t="n">
-        <v>0.05035109976920058</v>
+        <v>0.03823018883216525</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>0.04619210190876767</v>
+        <v>0.04984071370197334</v>
       </c>
       <c r="B160" t="n">
-        <v>0.04686945384536616</v>
+        <v>0.03589470906315323</v>
       </c>
       <c r="C160" t="n">
-        <v>0.08762562337541721</v>
+        <v>0.1758350999393155</v>
       </c>
       <c r="D160" t="n">
-        <v>0.3647612310343614</v>
+        <v>0.2882410650967825</v>
       </c>
       <c r="E160" t="n">
-        <v>0.3494232415479075</v>
+        <v>0.3297331834432159</v>
       </c>
       <c r="F160" t="n">
-        <v>0.05474560429875796</v>
+        <v>0.08219351304751812</v>
       </c>
       <c r="G160" t="n">
-        <v>0.05038274398942139</v>
+        <v>0.03826171570804142</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>0.04623318892349915</v>
+        <v>0.04998866983689701</v>
       </c>
       <c r="B161" t="n">
-        <v>0.04687796400387238</v>
+        <v>0.03593428633725917</v>
       </c>
       <c r="C161" t="n">
-        <v>0.08760078981979401</v>
+        <v>0.1757474047560864</v>
       </c>
       <c r="D161" t="n">
-        <v>0.3646371966996098</v>
+        <v>0.2878404912062476</v>
       </c>
       <c r="E161" t="n">
-        <v>0.3494869713354675</v>
+        <v>0.3297315396415552</v>
       </c>
       <c r="F161" t="n">
-        <v>0.05475063826974326</v>
+        <v>0.08246435194989853</v>
       </c>
       <c r="G161" t="n">
-        <v>0.05041325094801724</v>
+        <v>0.03829325627205618</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>0.04627363951513674</v>
+        <v>0.05013232530670735</v>
       </c>
       <c r="B162" t="n">
-        <v>0.04688569128503634</v>
+        <v>0.03597392630806022</v>
       </c>
       <c r="C162" t="n">
-        <v>0.08757687354539588</v>
+        <v>0.1756537296321138</v>
       </c>
       <c r="D162" t="n">
-        <v>0.3644976199961898</v>
+        <v>0.2874299003814744</v>
       </c>
       <c r="E162" t="n">
-        <v>0.3495683992138783</v>
+        <v>0.3297517701641529</v>
       </c>
       <c r="F162" t="n">
-        <v>0.05475509869924025</v>
+        <v>0.08273354794210219</v>
       </c>
       <c r="G162" t="n">
-        <v>0.05044267774512401</v>
+        <v>0.03832480026538937</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>0.04631344525322683</v>
+        <v>0.05027182336818745</v>
       </c>
       <c r="B163" t="n">
-        <v>0.04689268247152867</v>
+        <v>0.03601363727981495</v>
       </c>
       <c r="C163" t="n">
-        <v>0.08755389250832817</v>
+        <v>0.175554765936415</v>
       </c>
       <c r="D163" t="n">
-        <v>0.3643439687459482</v>
+        <v>0.2870199426330016</v>
       </c>
       <c r="E163" t="n">
-        <v>0.3496659278290242</v>
+        <v>0.3297829100353186</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0547590076985334</v>
+        <v>0.08300058303448388</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0504710754934047</v>
+        <v>0.03835633771277833</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>0.04635259868525055</v>
+        <v>0.05040734523937264</v>
       </c>
       <c r="B164" t="n">
-        <v>0.04689898681666879</v>
+        <v>0.03605338948343883</v>
       </c>
       <c r="C164" t="n">
-        <v>0.08753185977089964</v>
+        <v>0.1754512068495401</v>
       </c>
       <c r="D164" t="n">
-        <v>0.3641776570214715</v>
+        <v>0.2866195583363534</v>
       </c>
       <c r="E164" t="n">
-        <v>0.3497780244719791</v>
+        <v>0.3298156650323708</v>
       </c>
       <c r="F164" t="n">
-        <v>0.05476238364335798</v>
+        <v>0.0832649767789624</v>
       </c>
       <c r="G164" t="n">
-        <v>0.05049848959036948</v>
+        <v>0.03838785827996141</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>0.04639109329088359</v>
+        <v>0.05053910257869532</v>
       </c>
       <c r="B165" t="n">
-        <v>0.04690465483411043</v>
+        <v>0.03609311858110197</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0875107827978597</v>
+        <v>0.1753437485017698</v>
       </c>
       <c r="D165" t="n">
-        <v>0.3640000447907967</v>
+        <v>0.2862359012385803</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3499032211872196</v>
+        <v>0.3298424846995737</v>
       </c>
       <c r="F165" t="n">
-        <v>0.05476524295287892</v>
+        <v>0.08352629407799925</v>
       </c>
       <c r="G165" t="n">
-        <v>0.050524960146245</v>
+        <v>0.03841935032227993</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>0.04642892338382852</v>
+        <v>0.05066732990918271</v>
       </c>
       <c r="B166" t="n">
-        <v>0.04690973723495904</v>
+        <v>0.03613273018368621</v>
       </c>
       <c r="C166" t="n">
-        <v>0.08749066288864564</v>
+        <v>0.175233088723229</v>
       </c>
       <c r="D166" t="n">
-        <v>0.3638124473233597</v>
+        <v>0.2858743699150515</v>
       </c>
       <c r="E166" t="n">
-        <v>0.3500401051776579</v>
+        <v>0.3298575317691493</v>
       </c>
       <c r="F166" t="n">
-        <v>0.05476760147753057</v>
+        <v>0.08378414969551076</v>
       </c>
       <c r="G166" t="n">
-        <v>0.05055052251402121</v>
+        <v>0.03845079980419057</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>0.0464660839925558</v>
+        <v>0.0507922773367106</v>
       </c>
       <c r="B167" t="n">
-        <v>0.04691428403797225</v>
+        <v>0.03617210522654694</v>
       </c>
       <c r="C167" t="n">
-        <v>0.08747149480338973</v>
+        <v>0.1751199234901044</v>
       </c>
       <c r="D167" t="n">
-        <v>0.3636161505377245</v>
+        <v>0.2855387334075689</v>
       </c>
       <c r="E167" t="n">
-        <v>0.3501873032111915</v>
+        <v>0.3298565617223313</v>
       </c>
       <c r="F167" t="n">
-        <v>0.05476947550828769</v>
+        <v>0.08403820955761571</v>
       </c>
       <c r="G167" t="n">
-        <v>0.05057520790888381</v>
+        <v>0.03848218925912195</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>0.04650257072770456</v>
+        <v>0.05091420375464335</v>
       </c>
       <c r="B168" t="n">
-        <v>0.04691834382948581</v>
+        <v>0.03621110602880289</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0874532666878253</v>
+        <v>0.175004941219763</v>
       </c>
       <c r="D168" t="n">
-        <v>0.3634124280830823</v>
+        <v>0.2852313331397426</v>
       </c>
       <c r="E168" t="n">
-        <v>0.3503434641918758</v>
+        <v>0.3298367298995141</v>
       </c>
       <c r="F168" t="n">
-        <v>0.05477088241709608</v>
+        <v>0.08428818902964517</v>
       </c>
       <c r="G168" t="n">
-        <v>0.05059904406291955</v>
+        <v>0.03851349692788899</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>0.04653837966236157</v>
+        <v>0.05103337075755638</v>
       </c>
       <c r="B169" t="n">
-        <v>0.0469219631879655</v>
+        <v>0.03624958280887385</v>
       </c>
       <c r="C169" t="n">
-        <v>0.08743596027088706</v>
+        <v>0.1748888152819173</v>
       </c>
       <c r="D169" t="n">
-        <v>0.3632025565586044</v>
+        <v>0.2849533404607136</v>
       </c>
       <c r="E169" t="n">
-        <v>0.3505072434251704</v>
+        <v>0.3297963457516049</v>
       </c>
       <c r="F169" t="n">
-        <v>0.05477184099455738</v>
+        <v>0.08453384876015627</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0506220559004544</v>
+        <v>0.03854469617917795</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>0.04657350722140137</v>
+        <v>0.05115003735535913</v>
       </c>
       <c r="B170" t="n">
-        <v>0.04692518623401003</v>
+        <v>0.03628738038896621</v>
       </c>
       <c r="C170" t="n">
-        <v>0.08741955145463862</v>
+        <v>0.174772195090292</v>
       </c>
       <c r="D170" t="n">
-        <v>0.3629878258063848</v>
+        <v>0.2847050484277748</v>
       </c>
       <c r="E170" t="n">
-        <v>0.3506772915888945</v>
+        <v>0.3297345946993484</v>
       </c>
       <c r="F170" t="n">
-        <v>0.05477237151962143</v>
+        <v>0.08477498877559976</v>
       </c>
       <c r="G170" t="n">
-        <v>0.05064426617504402</v>
+        <v>0.03857575526265949</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0.04660795009183611</v>
+        <v>0.05126445556668793</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0469280543072173</v>
+        <v>0.03632434480415202</v>
       </c>
       <c r="C171" t="n">
-        <v>0.08740401114178072</v>
+        <v>0.1746556963001213</v>
       </c>
       <c r="D171" t="n">
-        <v>0.3627695428877652</v>
+        <v>0.2844861766946331</v>
       </c>
       <c r="E171" t="n">
-        <v>0.3508522498725841</v>
+        <v>0.3296512475092956</v>
       </c>
       <c r="F171" t="n">
-        <v>0.05477249564546927</v>
+        <v>0.0850114417056969</v>
       </c>
       <c r="G171" t="n">
-        <v>0.05066569605334517</v>
+        <v>0.03860663741941334</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>0.04664170516503186</v>
+        <v>0.05137686685236195</v>
       </c>
       <c r="B172" t="n">
-        <v>0.04693060575253424</v>
+        <v>0.0363603295123852</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0873893062939094</v>
+        <v>0.1745398905337907</v>
       </c>
       <c r="D172" t="n">
-        <v>0.3625490289635797</v>
+        <v>0.284296170006996</v>
       </c>
       <c r="E172" t="n">
-        <v>0.3510307520163453</v>
+        <v>0.329546375788967</v>
       </c>
       <c r="F172" t="n">
-        <v>0.05477223617983915</v>
+        <v>0.085243065986956</v>
       </c>
       <c r="G172" t="n">
-        <v>0.05068636562875644</v>
+        <v>0.03863730131854324</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>0.04667476949366992</v>
+        <v>0.05148749938353666</v>
       </c>
       <c r="B173" t="n">
-        <v>0.04693287578763154</v>
+        <v>0.03639520091609628</v>
       </c>
       <c r="C173" t="n">
-        <v>0.08737540106521637</v>
+        <v>0.1744252951897073</v>
       </c>
       <c r="D173" t="n">
-        <v>0.3623276099962765</v>
+        <v>0.2841344732227698</v>
       </c>
       <c r="E173" t="n">
-        <v>0.3512114325129667</v>
+        <v>0.3294200895814325</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0547716168062669</v>
+        <v>0.08546973991380774</v>
       </c>
       <c r="G173" t="n">
-        <v>0.05070629433797831</v>
+        <v>0.03866770179264974</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>0.04670714027469327</v>
+        <v>0.05159656601571</v>
       </c>
       <c r="B174" t="n">
-        <v>0.0469348964406645</v>
+        <v>0.03642884292529756</v>
       </c>
       <c r="C174" t="n">
-        <v>0.08736225800508411</v>
+        <v>0.1743123636597049</v>
       </c>
       <c r="D174" t="n">
-        <v>0.362106602431352</v>
+        <v>0.2840007688355551</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3513929397420529</v>
+        <v>0.3292723106006875</v>
       </c>
       <c r="F174" t="n">
-        <v>0.05477066181600398</v>
+        <v>0.08569135717542239</v>
       </c>
       <c r="G174" t="n">
-        <v>0.05072550129014589</v>
+        <v>0.03869779078762293</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>0.0467388148346824</v>
+        <v>0.05170426287054972</v>
       </c>
       <c r="B175" t="n">
-        <v>0.04693669652845821</v>
+        <v>0.03646116039431797</v>
       </c>
       <c r="C175" t="n">
-        <v>0.08734983912041856</v>
+        <v>0.1742014765356967</v>
       </c>
       <c r="D175" t="n">
-        <v>0.3618872960546992</v>
+        <v>0.2838951658313547</v>
       </c>
       <c r="E175" t="n">
-        <v>0.3515739521023235</v>
+        <v>0.3291025916073425</v>
       </c>
       <c r="F175" t="n">
-        <v>0.05476939586571539</v>
+        <v>0.08590782427984854</v>
       </c>
       <c r="G175" t="n">
-        <v>0.05074400549370042</v>
+        <v>0.03872751848088991</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>0.04676979063102133</v>
+        <v>0.05181076844655492</v>
       </c>
       <c r="B176" t="n">
-        <v>0.04693830167838173</v>
+        <v>0.03649208126711939</v>
       </c>
       <c r="C176" t="n">
-        <v>0.08733810680301607</v>
+        <v>0.1740929342056918</v>
       </c>
       <c r="D176" t="n">
-        <v>0.361670935844778</v>
+        <v>0.28381833181264</v>
       </c>
       <c r="E176" t="n">
-        <v>0.3517531952300826</v>
+        <v>0.3289099897497271</v>
       </c>
       <c r="F176" t="n">
-        <v>0.05476784380221748</v>
+        <v>0.08611906007028329</v>
       </c>
       <c r="G176" t="n">
-        <v>0.05076182601050216</v>
+        <v>0.03875683444798367</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>0.0468000652612835</v>
+        <v>0.051916243066831</v>
       </c>
       <c r="B177" t="n">
-        <v>0.04693973437969987</v>
+        <v>0.03652155749620092</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0873270245504225</v>
+        <v>0.1739869513162731</v>
       </c>
       <c r="D177" t="n">
-        <v>0.3614587046109229</v>
+        <v>0.2837715632848611</v>
       </c>
       <c r="E177" t="n">
-        <v>0.3519294586103546</v>
+        <v>0.3286929988914041</v>
       </c>
       <c r="F177" t="n">
-        <v>0.05476603054659495</v>
+        <v>0.08632499707115524</v>
       </c>
       <c r="G177" t="n">
-        <v>0.05077898204072297</v>
+        <v>0.03878568887327447</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>0.04682963647804851</v>
+        <v>0.05202082862418222</v>
       </c>
       <c r="B178" t="n">
-        <v>0.04694101406188355</v>
+        <v>0.03654956471175359</v>
       </c>
       <c r="C178" t="n">
-        <v>0.08731655747859991</v>
+        <v>0.1738836535034987</v>
       </c>
       <c r="D178" t="n">
-        <v>0.361251707787584</v>
+        <v>0.2837567921572804</v>
       </c>
       <c r="E178" t="n">
-        <v>0.3521016102210226</v>
+        <v>0.3284495429345763</v>
       </c>
       <c r="F178" t="n">
-        <v>0.05476398102166054</v>
+        <v>0.0865255843998677</v>
       </c>
       <c r="G178" t="n">
-        <v>0.05079549295118309</v>
+        <v>0.03881403366884129</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0.0468585022124081</v>
+        <v>0.05212464850287243</v>
       </c>
       <c r="B179" t="n">
-        <v>0.04694215720345404</v>
+        <v>0.03657610084466304</v>
       </c>
       <c r="C179" t="n">
-        <v>0.08730667264164198</v>
+        <v>0.1737830766090462</v>
       </c>
       <c r="D179" t="n">
-        <v>0.3610509611360626</v>
+        <v>0.2837765299505306</v>
       </c>
       <c r="E179" t="n">
-        <v>0.352268608449027</v>
+        <v>0.3281770289022646</v>
       </c>
       <c r="F179" t="n">
-        <v>0.0547617200984599</v>
+        <v>0.08672079168651145</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0508113782589512</v>
+        <v>0.03884182350411166</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0.04688666060900714</v>
+        <v>0.05222780760470192</v>
       </c>
       <c r="B180" t="n">
-        <v>0.046943177473729</v>
+        <v>0.03660118386902293</v>
       </c>
       <c r="C180" t="n">
-        <v>0.08729733919383775</v>
+        <v>0.173685168596061</v>
       </c>
       <c r="D180" t="n">
-        <v>0.3608573815669044</v>
+        <v>0.2838337546591138</v>
       </c>
       <c r="E180" t="n">
-        <v>0.3524295110445438</v>
+        <v>0.3278724551583885</v>
       </c>
       <c r="F180" t="n">
-        <v>0.05475927253352206</v>
+        <v>0.08691061342914502</v>
       </c>
       <c r="G180" t="n">
-        <v>0.05082665757844231</v>
+        <v>0.0388690166835669</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>0.04691411008694923</v>
+        <v>0.05233039246194643</v>
       </c>
       <c r="B181" t="n">
-        <v>0.04694408594136394</v>
+        <v>0.03662484891369353</v>
       </c>
       <c r="C181" t="n">
-        <v>0.08728852845773495</v>
+        <v>0.1735897941253073</v>
       </c>
       <c r="D181" t="n">
-        <v>0.3606717807578669</v>
+        <v>0.2839317486532863</v>
       </c>
       <c r="E181" t="n">
-        <v>0.3525834813031981</v>
+        <v>0.3275325667098575</v>
       </c>
       <c r="F181" t="n">
-        <v>0.05475666288475797</v>
+        <v>0.08709507325564766</v>
       </c>
       <c r="G181" t="n">
-        <v>0.05084135056813083</v>
+        <v>0.03889557588026171</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>0.04694084940657662</v>
+        <v>0.05243247136802302</v>
       </c>
       <c r="B182" t="n">
-        <v>0.04694489129901422</v>
+        <v>0.03664714500428126</v>
       </c>
       <c r="C182" t="n">
-        <v>0.08728021391228678</v>
+        <v>0.1734967416113233</v>
       </c>
       <c r="D182" t="n">
-        <v>0.3604948611460826</v>
+        <v>0.2840738989063736</v>
       </c>
       <c r="E182" t="n">
-        <v>0.352729792047694</v>
+        <v>0.32715404679001</v>
       </c>
       <c r="F182" t="n">
-        <v>0.05475391535758602</v>
+        <v>0.08727422757049842</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0508554768307636</v>
+        <v>0.03892146874949028</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>0.04696687777409116</v>
+        <v>0.05253409457393049</v>
       </c>
       <c r="B183" t="n">
-        <v>0.04694560017506622</v>
+        <v>0.03666813167312177</v>
       </c>
       <c r="C183" t="n">
-        <v>0.08727237117738129</v>
+        <v>0.1734057324818476</v>
       </c>
       <c r="D183" t="n">
-        <v>0.3603272135159081</v>
+        <v>0.2842634729095657</v>
       </c>
       <c r="E183" t="n">
-        <v>0.3528678278995375</v>
+        <v>0.3267337316717401</v>
       </c>
       <c r="F183" t="n">
-        <v>0.05475105361446274</v>
+        <v>0.08744816825829382</v>
       </c>
       <c r="G183" t="n">
-        <v>0.05086905584354685</v>
+        <v>0.03894666843149996</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>0.04699219493234701</v>
+        <v>0.05263529455261594</v>
       </c>
       <c r="B184" t="n">
-        <v>0.04694621745284568</v>
+        <v>0.03668787568376704</v>
       </c>
       <c r="C184" t="n">
-        <v>0.08726497797912684</v>
+        <v>0.1733164321390978</v>
       </c>
       <c r="D184" t="n">
-        <v>0.3601693156426751</v>
+        <v>0.2845033847445836</v>
       </c>
       <c r="E184" t="n">
-        <v>0.3529970866573924</v>
+        <v>0.3262688347042392</v>
       </c>
       <c r="F184" t="n">
-        <v>0.05474810048792417</v>
+        <v>0.08761702418518867</v>
       </c>
       <c r="G184" t="n">
-        <v>0.05088210684767742</v>
+        <v>0.03897115399050766</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0.04701680129311828</v>
+        <v>0.05273608636492408</v>
       </c>
       <c r="B185" t="n">
-        <v>0.04694674666209973</v>
+        <v>0.03670644807187785</v>
       </c>
       <c r="C185" t="n">
-        <v>0.08725801417275647</v>
+        <v>0.1732284621761133</v>
       </c>
       <c r="D185" t="n">
-        <v>0.3600215314224148</v>
+        <v>0.2847959656157301</v>
       </c>
       <c r="E185" t="n">
-        <v>0.3531171799783966</v>
+        <v>0.3257571655872157</v>
       </c>
       <c r="F185" t="n">
-        <v>0.05474507768801606</v>
+        <v>0.08778096137408546</v>
       </c>
       <c r="G185" t="n">
-        <v>0.05089464878320734</v>
+        <v>0.03899491081005333</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0.04704069805697908</v>
+        <v>0.05283646817339598</v>
       </c>
       <c r="B186" t="n">
-        <v>0.04694719037427521</v>
+        <v>0.03672392164008139</v>
       </c>
       <c r="C186" t="n">
-        <v>0.08725146176752673</v>
+        <v>0.1731414132832077</v>
       </c>
       <c r="D186" t="n">
-        <v>0.3598841104569446</v>
+        <v>0.285142752018473</v>
       </c>
       <c r="E186" t="n">
-        <v>0.3532278336579793</v>
+        <v>0.3251973320715197</v>
       </c>
       <c r="F186" t="n">
-        <v>0.05474200547022665</v>
+        <v>0.08794018186366682</v>
       </c>
       <c r="G186" t="n">
-        <v>0.05090670021607042</v>
+        <v>0.0390179309496558</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0.04706388732732599</v>
+        <v>0.05293642195443672</v>
       </c>
       <c r="B187" t="n">
-        <v>0.04694755059863401</v>
+        <v>0.03674036903005843</v>
       </c>
       <c r="C187" t="n">
-        <v>0.08724530496945482</v>
+        <v>0.1730548582061215</v>
       </c>
       <c r="D187" t="n">
-        <v>0.3597571881226531</v>
+        <v>0.2855443027681731</v>
       </c>
       <c r="E187" t="n">
-        <v>0.353328887393458</v>
+        <v>0.3245889132295512</v>
       </c>
       <c r="F187" t="n">
-        <v>0.05473890231051702</v>
+        <v>0.08809492133337223</v>
       </c>
       <c r="G187" t="n">
-        <v>0.05091827927795232</v>
+        <v>0.03904021347828673</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0.04708637221218978</v>
+        <v>0.05303591441664907</v>
       </c>
       <c r="B188" t="n">
-        <v>0.04694782916557293</v>
+        <v>0.0367558613901641</v>
       </c>
       <c r="C188" t="n">
-        <v>0.08723953019917519</v>
+        <v>0.1729683643134848</v>
       </c>
       <c r="D188" t="n">
-        <v>0.3596407864476583</v>
+        <v>0.2860000535595429</v>
       </c>
       <c r="E188" t="n">
-        <v>0.3534202937229162</v>
+        <v>0.3239325959250327</v>
       </c>
       <c r="F188" t="n">
-        <v>0.05473578462603356</v>
+        <v>0.08824544564361284</v>
       </c>
       <c r="G188" t="n">
-        <v>0.05092940362645195</v>
+        <v>0.03906176475151376</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>0.04710815689543192</v>
+        <v>0.05313489815571987</v>
       </c>
       <c r="B189" t="n">
-        <v>0.04694802805420818</v>
+        <v>0.03677046763379287</v>
       </c>
       <c r="C189" t="n">
-        <v>0.08723412609634221</v>
+        <v>0.1728815051930773</v>
       </c>
       <c r="D189" t="n">
-        <v>0.3595348162214648</v>
+        <v>0.2865082152608546</v>
       </c>
       <c r="E189" t="n">
-        <v>0.3535021157755331</v>
+        <v>0.3232302686536706</v>
       </c>
       <c r="F189" t="n">
-        <v>0.05473266655178233</v>
+        <v>0.08839204649658798</v>
       </c>
       <c r="G189" t="n">
-        <v>0.05094009040524347</v>
+        <v>0.03908259860629681</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>0.04712924668291595</v>
+        <v>0.05323331303420326</v>
       </c>
       <c r="B190" t="n">
-        <v>0.04694814967465881</v>
+        <v>0.03678425418785967</v>
       </c>
       <c r="C190" t="n">
-        <v>0.08722908345990651</v>
+        <v>0.1727938709867562</v>
       </c>
       <c r="D190" t="n">
-        <v>0.3594390808782677</v>
+        <v>0.2870657196313152</v>
       </c>
       <c r="E190" t="n">
-        <v>0.353574523258262</v>
+        <v>0.3224850693131134</v>
       </c>
       <c r="F190" t="n">
-        <v>0.05472955981824144</v>
+        <v>0.0885350364359824</v>
       </c>
       <c r="G190" t="n">
-        <v>0.05095035622776015</v>
+        <v>0.03910273641076981</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>0.04714964801600172</v>
+        <v>0.05333108778828213</v>
       </c>
       <c r="B191" t="n">
-        <v>0.04694819706749521</v>
+        <v>0.03679728514254867</v>
       </c>
       <c r="C191" t="n">
-        <v>0.08722439509706113</v>
+        <v>0.1727050771254148</v>
       </c>
       <c r="D191" t="n">
-        <v>0.3593532824569147</v>
+        <v>0.2876682139768416</v>
       </c>
       <c r="E191" t="n">
-        <v>0.353637786462781</v>
+        <v>0.3217013856148922</v>
       </c>
       <c r="F191" t="n">
-        <v>0.05472647373843127</v>
+        <v>0.08867474341423782</v>
       </c>
       <c r="G191" t="n">
-        <v>0.05096021716131092</v>
+        <v>0.03912220693778262</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>0.04716936845294484</v>
+        <v>0.05342814179537415</v>
       </c>
       <c r="B192" t="n">
-        <v>0.0469481740338832</v>
+        <v>0.03680962265553275</v>
       </c>
       <c r="C192" t="n">
-        <v>0.08722005557955016</v>
+        <v>0.1726147714047918</v>
       </c>
       <c r="D192" t="n">
-        <v>0.3592770299149434</v>
+        <v>0.2883101043700587</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3536922679752725</v>
+        <v>0.3208848086606972</v>
       </c>
       <c r="F192" t="n">
-        <v>0.05472341531659365</v>
+        <v>0.08881150509799263</v>
       </c>
       <c r="G192" t="n">
-        <v>0.05096968872681903</v>
+        <v>0.03914104601555286</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>0.04718841662225115</v>
+        <v>0.05352438697666945</v>
       </c>
       <c r="B193" t="n">
-        <v>0.04694808518826744</v>
+        <v>0.03682132745522411</v>
       </c>
       <c r="C193" t="n">
-        <v>0.0872160609020229</v>
+        <v>0.1725226392718943</v>
       </c>
       <c r="D193" t="n">
-        <v>0.3592098499959334</v>
+        <v>0.2889846455209348</v>
       </c>
       <c r="E193" t="n">
-        <v>0.3537384119101144</v>
+        <v>0.3200420416909877</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0547203894754696</v>
+        <v>0.08894566316418763</v>
       </c>
       <c r="G193" t="n">
-        <v>0.05097878590593992</v>
+        <v>0.03915929592010176</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>0.04720680213408435</v>
+        <v>0.05361972975553108</v>
       </c>
       <c r="B194" t="n">
-        <v>0.04694793591499807</v>
+        <v>0.03683245930068321</v>
       </c>
       <c r="C194" t="n">
-        <v>0.08721240801906865</v>
+        <v>0.1724284075537528</v>
       </c>
       <c r="D194" t="n">
-        <v>0.359151200353545</v>
+        <v>0.2896840737103112</v>
       </c>
       <c r="E194" t="n">
-        <v>0.3537767310816646</v>
+        <v>0.319180767483864</v>
       </c>
       <c r="F194" t="n">
-        <v>0.05471739936890115</v>
+        <v>0.08907755769820196</v>
       </c>
       <c r="G194" t="n">
-        <v>0.05098752312773781</v>
+        <v>0.0391770044976554</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>0.0472245354902286</v>
+        <v>0.05371407303633959</v>
       </c>
       <c r="B195" t="n">
-        <v>0.04694773228657882</v>
+        <v>0.03684307727248561</v>
       </c>
       <c r="C195" t="n">
-        <v>0.08720909433256267</v>
+        <v>0.1723318466208712</v>
       </c>
       <c r="D195" t="n">
-        <v>0.3591004846697011</v>
+        <v>0.2903997781475043</v>
       </c>
       <c r="E195" t="n">
-        <v>0.3538077921371502</v>
+        <v>0.3183094789842612</v>
       </c>
       <c r="F195" t="n">
-        <v>0.05471444679894918</v>
+        <v>0.08920752191008954</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0509959142848222</v>
+        <v>0.03919422402844884</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>0.04724162797644488</v>
+        <v>0.053807318126469</v>
       </c>
       <c r="B196" t="n">
-        <v>0.04694748092661698</v>
+        <v>0.03685323981362652</v>
       </c>
       <c r="C196" t="n">
-        <v>0.08720611713480547</v>
+        <v>0.1722327713004787</v>
       </c>
       <c r="D196" t="n">
-        <v>0.359057069249918</v>
+        <v>0.291122504846726</v>
       </c>
       <c r="E196" t="n">
-        <v>0.3538321992838785</v>
+        <v>0.3174372788019784</v>
       </c>
       <c r="F196" t="n">
-        <v>0.05471153268390279</v>
+        <v>0.08933587723969157</v>
       </c>
       <c r="G196" t="n">
-        <v>0.05100397274443876</v>
+        <v>0.03921100987102989</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>0.04725809154072166</v>
+        <v>0.05389936655702176</v>
       </c>
       <c r="B197" t="n">
-        <v>0.04694718882887765</v>
+        <v>0.03686300445179132</v>
       </c>
       <c r="C197" t="n">
-        <v>0.08720347301753137</v>
+        <v>0.1721310407262863</v>
       </c>
       <c r="D197" t="n">
-        <v>0.3590203004370336</v>
+        <v>0.2918425862370018</v>
       </c>
       <c r="E197" t="n">
-        <v>0.3538505772873374</v>
+        <v>0.3165736541116496</v>
       </c>
       <c r="F197" t="n">
-        <v>0.05470865753846178</v>
+        <v>0.08946292897942684</v>
       </c>
       <c r="G197" t="n">
-        <v>0.05101171135003167</v>
+        <v>0.03922741893682226</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>0.04727393867412252</v>
+        <v>0.05399012176185611</v>
       </c>
       <c r="B198" t="n">
-        <v>0.04694686316177869</v>
+        <v>0.0368724271867018</v>
       </c>
       <c r="C198" t="n">
-        <v>0.08720115732418997</v>
+        <v>0.1720265572000923</v>
       </c>
       <c r="D198" t="n">
-        <v>0.3589895221527085</v>
+        <v>0.2925501891371726</v>
       </c>
       <c r="E198" t="n">
-        <v>0.3538635543139751</v>
+        <v>0.3157282341259619</v>
       </c>
       <c r="F198" t="n">
-        <v>0.05470582194577785</v>
+        <v>0.08958896252295405</v>
       </c>
       <c r="G198" t="n">
-        <v>0.05101914242745299</v>
+        <v>0.03924350806526081</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>0.0472891822954057</v>
+        <v>0.05407949059022187</v>
       </c>
       <c r="B199" t="n">
-        <v>0.04694651107569</v>
+        <v>0.03688156158580377</v>
       </c>
       <c r="C199" t="n">
-        <v>0.08719916366093836</v>
+        <v>0.1719192643034333</v>
       </c>
       <c r="D199" t="n">
-        <v>0.3589640927137334</v>
+        <v>0.2932355730483311</v>
       </c>
       <c r="E199" t="n">
-        <v>0.3538717454699605</v>
+        <v>0.3149105378027512</v>
       </c>
       <c r="F199" t="n">
-        <v>0.05470302698749102</v>
+        <v>0.08971424027151184</v>
       </c>
       <c r="G199" t="n">
-        <v>0.05102627779678418</v>
+        <v>0.03925933239794683</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>0.04730383564718071</v>
+        <v>0.05416738461666996</v>
       </c>
       <c r="B200" t="n">
-        <v>0.04694613951095187</v>
+        <v>0.03689045765131236</v>
       </c>
       <c r="C200" t="n">
-        <v>0.08719748351049224</v>
+        <v>0.171809144383501</v>
       </c>
       <c r="D200" t="n">
-        <v>0.3589434001940862</v>
+        <v>0.2938893505633965</v>
       </c>
       <c r="E200" t="n">
-        <v>0.3538757377546704</v>
+        <v>0.314129719754479</v>
       </c>
       <c r="F200" t="n">
-        <v>0.05470027460545281</v>
+        <v>0.08983899919798113</v>
       </c>
       <c r="G200" t="n">
-        <v>0.05103312877716551</v>
+        <v>0.03927494383266025</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>0.04731791220239544</v>
+        <v>0.05425372128513262</v>
       </c>
       <c r="B201" t="n">
-        <v>0.04694575503842054</v>
+        <v>0.0368991605399281</v>
       </c>
       <c r="C201" t="n">
-        <v>0.08719610596499783</v>
+        <v>0.1716962153701706</v>
       </c>
       <c r="D201" t="n">
-        <v>0.3589268755939456</v>
+        <v>0.2945027415970922</v>
       </c>
       <c r="E201" t="n">
-        <v>0.3538760771243313</v>
+        <v>0.3133943223596665</v>
       </c>
       <c r="F201" t="n">
-        <v>0.05469756787475127</v>
+        <v>0.08996344919645466</v>
       </c>
       <c r="G201" t="n">
-        <v>0.05103970620116451</v>
+        <v>0.03929038965155554</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0.04733142558576052</v>
+        <v>0.05433842486279736</v>
       </c>
       <c r="B202" t="n">
-        <v>0.0469453637177908</v>
+        <v>0.03690770928158726</v>
       </c>
       <c r="C202" t="n">
-        <v>0.08719501759106477</v>
+        <v>0.1715805271451217</v>
       </c>
       <c r="D202" t="n">
-        <v>0.3589140032393112</v>
+        <v>0.2950678133893996</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3538732582689131</v>
+        <v>0.3127120418358791</v>
       </c>
       <c r="F202" t="n">
-        <v>0.05469491117688496</v>
+        <v>0.09008777207708342</v>
       </c>
       <c r="G202" t="n">
-        <v>0.0510460204202711</v>
+        <v>0.03930571140813148</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>0.04734438950611867</v>
+        <v>0.05442142723448679</v>
       </c>
       <c r="B203" t="n">
-        <v>0.04694497100908616</v>
+        <v>0.03691613559929743</v>
       </c>
       <c r="C203" t="n">
-        <v>0.08719420243163792</v>
+        <v>0.171462157516559</v>
       </c>
       <c r="D203" t="n">
-        <v>0.3589043279204069</v>
+        <v>0.2955776986111436</v>
       </c>
       <c r="E203" t="n">
-        <v>0.3538677175419228</v>
+        <v>0.312089515677912</v>
       </c>
       <c r="F203" t="n">
-        <v>0.05469231026648265</v>
+        <v>0.09021212123048734</v>
       </c>
       <c r="G203" t="n">
-        <v>0.05105208132434658</v>
+        <v>0.03932094413011366</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0.04735681770261633</v>
+        <v>0.0545026685492306</v>
       </c>
       <c r="B204" t="n">
-        <v>0.0469445817133468</v>
+        <v>0.03692446298025832</v>
       </c>
       <c r="C204" t="n">
-        <v>0.08719364214009059</v>
+        <v>0.171341207995158</v>
       </c>
       <c r="D204" t="n">
-        <v>0.358897458553985</v>
+        <v>0.2960267845851869</v>
       </c>
       <c r="E204" t="n">
-        <v>0.3538598292992097</v>
+        <v>0.3115321381786326</v>
       </c>
       <c r="F204" t="n">
-        <v>0.05468977223636892</v>
+        <v>0.09033662181826733</v>
       </c>
       <c r="G204" t="n">
-        <v>0.05105789835438228</v>
+        <v>0.0393361158932664</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0.04736872390628605</v>
+        <v>0.05458209774064968</v>
       </c>
       <c r="B205" t="n">
-        <v>0.04694419995786314</v>
+        <v>0.03693270607757499</v>
       </c>
       <c r="C205" t="n">
-        <v>0.08719331623050884</v>
+        <v>0.1712177995025707</v>
       </c>
       <c r="D205" t="n">
-        <v>0.3588930682573587</v>
+        <v>0.296410867342473</v>
       </c>
       <c r="E205" t="n">
-        <v>0.3538499057290679</v>
+        <v>0.3110439101158132</v>
       </c>
       <c r="F205" t="n">
-        <v>0.05468730539623742</v>
+        <v>0.09046137144485819</v>
       </c>
       <c r="G205" t="n">
-        <v>0.05106348052267824</v>
+        <v>0.03935124777606036</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0.04738012180908087</v>
+        <v>0.05465967293793871</v>
       </c>
       <c r="B206" t="n">
-        <v>0.04694382921566898</v>
+        <v>0.03694087053543531</v>
       </c>
       <c r="C206" t="n">
-        <v>0.08719320242240623</v>
+        <v>0.1710920682602432</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3588908911068492</v>
+        <v>0.2967272651376398</v>
       </c>
       <c r="E206" t="n">
-        <v>0.3538381999427289</v>
+        <v>0.3106273277549177</v>
       </c>
       <c r="F206" t="n">
-        <v>0.05468491907041158</v>
+        <v>0.09058644117614766</v>
       </c>
       <c r="G206" t="n">
-        <v>0.05106883643285292</v>
+        <v>0.03936635419767771</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0.04739102504249643</v>
+        <v>0.05473536175009119</v>
       </c>
       <c r="B207" t="n">
-        <v>0.04694347235563023</v>
+        <v>0.03694895325640284</v>
       </c>
       <c r="C207" t="n">
-        <v>0.08719327705634758</v>
+        <v>0.1709641621366624</v>
       </c>
       <c r="D207" t="n">
-        <v>0.3588907159732281</v>
+        <v>0.2969748870095065</v>
       </c>
       <c r="E207" t="n">
-        <v>0.3538249119320301</v>
+        <v>0.3102833154770889</v>
       </c>
       <c r="F207" t="n">
-        <v>0.05468262333725316</v>
+        <v>0.0907118767785873</v>
       </c>
       <c r="G207" t="n">
-        <v>0.05107397430300947</v>
+        <v>0.03938144359166106</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>0.04740144716361225</v>
+        <v>0.05480914144625751</v>
       </c>
       <c r="B208" t="n">
-        <v>0.04694313171452145</v>
+        <v>0.03695694311381099</v>
       </c>
       <c r="C208" t="n">
-        <v>0.08719351555415997</v>
+        <v>0.1708342375895505</v>
       </c>
       <c r="D208" t="n">
-        <v>0.3588923780698248</v>
+        <v>0.2971542531645736</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3538101967782837</v>
+        <v>0.3100112052068862</v>
       </c>
       <c r="F208" t="n">
-        <v>0.05468042872786422</v>
+        <v>0.09083770011197091</v>
       </c>
       <c r="G208" t="n">
-        <v>0.05107890199173838</v>
+        <v>0.03939651936695021</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>0.04741140164737793</v>
+        <v>0.05488099899574143</v>
       </c>
       <c r="B209" t="n">
-        <v>0.04694280918204893</v>
+        <v>0.03696482204202244</v>
       </c>
       <c r="C209" t="n">
-        <v>0.08719389289906877</v>
+        <v>0.1707024574902721</v>
       </c>
       <c r="D209" t="n">
-        <v>0.3588957489807565</v>
+        <v>0.2972674652364735</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3537941743608204</v>
+        <v>0.3098087646034663</v>
       </c>
       <c r="F209" t="n">
-        <v>0.05467834590300442</v>
+        <v>0.0909639105717092</v>
       </c>
       <c r="G209" t="n">
-        <v>0.05108362702692037</v>
+        <v>0.03941158106031521</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>0.04742090188599157</v>
+        <v>0.05495093095380264</v>
       </c>
       <c r="B210" t="n">
-        <v>0.04694250629108822</v>
+        <v>0.03697256643152678</v>
       </c>
       <c r="C210" t="n">
-        <v>0.08719438411460094</v>
+        <v>0.170568989880986</v>
       </c>
       <c r="D210" t="n">
-        <v>0.3589007259898228</v>
+        <v>0.297318126092573</v>
       </c>
       <c r="E210" t="n">
-        <v>0.353776939751752</v>
+        <v>0.3096722745317005</v>
       </c>
       <c r="F210" t="n">
-        <v>0.0546763853274422</v>
+        <v>0.09109048650911888</v>
       </c>
       <c r="G210" t="n">
-        <v>0.05108815663929801</v>
+        <v>0.03942662560029194</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0.04742996118776847</v>
+        <v>0.05501894320455161</v>
       </c>
       <c r="B211" t="n">
-        <v>0.04694222429846365</v>
+        <v>0.03698014869898072</v>
       </c>
       <c r="C211" t="n">
-        <v>0.08719496471538139</v>
+        <v>0.1704340076607235</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3589072215982293</v>
+        <v>0.2973112106622361</v>
       </c>
       <c r="E211" t="n">
-        <v>0.3537585734586452</v>
+        <v>0.3095966545174198</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0546745569483617</v>
+        <v>0.09121738668542044</v>
       </c>
       <c r="G211" t="n">
-        <v>0.05109249779314862</v>
+        <v>0.03944164857066786</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>0.04743859278947692</v>
+        <v>0.05508505052180684</v>
       </c>
       <c r="B212" t="n">
-        <v>0.04694196426173116</v>
+        <v>0.03698753892300244</v>
       </c>
       <c r="C212" t="n">
-        <v>0.08719561113223823</v>
+        <v>0.1702976891537826</v>
       </c>
       <c r="D212" t="n">
-        <v>0.3589151538217394</v>
+        <v>0.2972528913147218</v>
       </c>
       <c r="E212" t="n">
-        <v>0.3537391508581537</v>
+        <v>0.3095756330038012</v>
       </c>
       <c r="F212" t="n">
-        <v>0.05467286990841234</v>
+        <v>0.09134455170148982</v>
       </c>
       <c r="G212" t="n">
-        <v>0.05109665722824699</v>
+        <v>0.03945664538139531</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>0.04744680986685502</v>
+        <v>0.05514927596397851</v>
       </c>
       <c r="B213" t="n">
-        <v>0.04694172709450997</v>
+        <v>0.03699470642054388</v>
       </c>
       <c r="C213" t="n">
-        <v>0.08719630108413266</v>
+        <v>0.1701602192932389</v>
       </c>
       <c r="D213" t="n">
-        <v>0.3589244379970218</v>
+        <v>0.297150323463651</v>
       </c>
       <c r="E213" t="n">
-        <v>0.3537187501755062</v>
+        <v>0.3096019570936236</v>
       </c>
       <c r="F213" t="n">
-        <v>0.05467133228511491</v>
+        <v>0.09147190550396624</v>
       </c>
       <c r="G213" t="n">
-        <v>0.05110064149685923</v>
+        <v>0.03947161226099758</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>0.04745462555180852</v>
+        <v>0.05521165008582997</v>
       </c>
       <c r="B214" t="n">
-        <v>0.04694151360441377</v>
+        <v>0.03700162116277837</v>
       </c>
       <c r="C214" t="n">
-        <v>0.08719701389794818</v>
+        <v>0.1700217911849166</v>
       </c>
       <c r="D214" t="n">
-        <v>0.3589349804098732</v>
+        <v>0.2970113991948478</v>
       </c>
       <c r="E214" t="n">
-        <v>0.3536974586574969</v>
+        <v>0.3096676343960825</v>
       </c>
       <c r="F214" t="n">
-        <v>0.05466995087553844</v>
+        <v>0.09159935697980237</v>
       </c>
       <c r="G214" t="n">
-        <v>0.05110445700291889</v>
+        <v>0.03948654699574262</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>0.04746205295317224</v>
+        <v>0.05527221002062321</v>
       </c>
       <c r="B215" t="n">
-        <v>0.04694132451249618</v>
+        <v>0.03700825494488804</v>
       </c>
       <c r="C215" t="n">
-        <v>0.08719773078285477</v>
+        <v>0.1698826075665228</v>
       </c>
       <c r="D215" t="n">
-        <v>0.3589466739830531</v>
+        <v>0.2968444786243525</v>
       </c>
       <c r="E215" t="n">
-        <v>0.353675376701077</v>
+        <v>0.3097641976448216</v>
       </c>
       <c r="F215" t="n">
-        <v>0.05466873102757118</v>
+        <v>0.0917268018169875</v>
       </c>
       <c r="G215" t="n">
-        <v>0.05110811003977495</v>
+        <v>0.03950144938180407</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>0.0474691051783258</v>
+        <v>0.05533099840599037</v>
       </c>
       <c r="B216" t="n">
-        <v>0.04694116045667598</v>
+        <v>0.03701458227835758</v>
       </c>
       <c r="C216" t="n">
-        <v>0.08719843501330583</v>
+        <v>0.1697428819323065</v>
       </c>
       <c r="D216" t="n">
-        <v>0.358959396066671</v>
+        <v>0.2966581101522589</v>
       </c>
       <c r="E216" t="n">
-        <v>0.3536526199376884</v>
+        <v>0.30988298133808</v>
       </c>
       <c r="F216" t="n">
-        <v>0.05466767652283059</v>
+        <v>0.09185412453016306</v>
       </c>
       <c r="G216" t="n">
-        <v>0.05111160682450075</v>
+        <v>0.03951632136284357</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>0.04747579535204239</v>
+        <v>0.05538806223175773</v>
       </c>
       <c r="B217" t="n">
-        <v>0.04694102197542101</v>
+        <v>0.03702058099377951</v>
       </c>
       <c r="C217" t="n">
-        <v>0.08719911209048845</v>
+        <v>0.1696028388274537</v>
       </c>
       <c r="D217" t="n">
-        <v>0.358973008215042</v>
+        <v>0.2964607516041838</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3536293193431254</v>
+        <v>0.3100153986832516</v>
       </c>
       <c r="F217" t="n">
-        <v>0.0546667895026634</v>
+        <v>0.09198120077822694</v>
       </c>
       <c r="G217" t="n">
-        <v>0.05111495352122244</v>
+        <v>0.03953116688134663</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>0.04748213663987357</v>
+        <v>0.05544345162677001</v>
       </c>
       <c r="B218" t="n">
-        <v>0.04694090948175597</v>
+        <v>0.03702623255709003</v>
       </c>
       <c r="C218" t="n">
-        <v>0.08719974982421641</v>
+        <v>0.1694627131345003</v>
       </c>
       <c r="D218" t="n">
-        <v>0.3589873576373374</v>
+        <v>0.2962605043314611</v>
       </c>
       <c r="E218" t="n">
-        <v>0.3536056197066326</v>
+        <v>0.3101532069593309</v>
       </c>
       <c r="F218" t="n">
-        <v>0.05466607045229212</v>
+        <v>0.09210789992408341</v>
       </c>
       <c r="G218" t="n">
-        <v>0.05111815625788955</v>
+        <v>0.03954599146676421</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>0.04748814226283161</v>
+        <v>0.05549721862662659</v>
       </c>
       <c r="B219" t="n">
-        <v>0.04694082323844666</v>
+        <v>0.03703152216669202</v>
       </c>
       <c r="C219" t="n">
-        <v>0.08720033835092796</v>
+        <v>0.1693227481666193</v>
       </c>
       <c r="D219" t="n">
-        <v>0.3590022800286447</v>
+        <v>0.2960648716032764</v>
       </c>
       <c r="E219" t="n">
-        <v>0.3535816767544449</v>
+        <v>0.3102887500669609</v>
       </c>
       <c r="F219" t="n">
-        <v>0.0546655182266592</v>
+        <v>0.09223408773937378</v>
       </c>
       <c r="G219" t="n">
-        <v>0.05112122113804655</v>
+        <v>0.03956080163045062</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0.04749382550937324</v>
+        <v>0.05554941597836416</v>
       </c>
       <c r="B220" t="n">
-        <v>0.04694076332697324</v>
+        <v>0.03703643867919879</v>
       </c>
       <c r="C220" t="n">
-        <v>0.08720087009769703</v>
+        <v>0.1691831925212507</v>
       </c>
       <c r="D220" t="n">
-        <v>0.3590176033609214</v>
+        <v>0.2958805510999738</v>
       </c>
       <c r="E220" t="n">
-        <v>0.3535576533474221</v>
+        <v>0.3104151683565165</v>
       </c>
       <c r="F220" t="n">
-        <v>0.0546651301191417</v>
+        <v>0.09235962922188566</v>
       </c>
       <c r="G220" t="n">
-        <v>0.05112415423847462</v>
+        <v>0.03957560414281064</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0.04749919974006488</v>
+        <v>0.05560009602544218</v>
       </c>
       <c r="B221" t="n">
-        <v>0.04694072962157336</v>
+        <v>0.03704097442763247</v>
       </c>
       <c r="C221" t="n">
-        <v>0.08720133968838932</v>
+        <v>0.1690442958203027</v>
       </c>
       <c r="D221" t="n">
-        <v>0.3590331522194581</v>
+        <v>0.2957132690945127</v>
       </c>
       <c r="E221" t="n">
-        <v>0.3535337151673241</v>
+        <v>0.3105265679272561</v>
       </c>
       <c r="F221" t="n">
-        <v>0.05466490196475456</v>
+        <v>0.09248439143294723</v>
       </c>
       <c r="G221" t="n">
-        <v>0.05112696159843424</v>
+        <v>0.03959040527190659</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0.04750427838439499</v>
+        <v>0.05564930970330638</v>
       </c>
       <c r="B222" t="n">
-        <v>0.04694072177078994</v>
+        <v>0.03704512499941091</v>
       </c>
       <c r="C222" t="n">
-        <v>0.08720174379864398</v>
+        <v>0.1689063035978289</v>
       </c>
       <c r="D222" t="n">
-        <v>0.3590487522835475</v>
+        <v>0.2955676612622957</v>
       </c>
       <c r="E222" t="n">
-        <v>0.3535100262911868</v>
+        <v>0.3106181441442621</v>
       </c>
       <c r="F222" t="n">
-        <v>0.05466482827052697</v>
+        <v>0.09260824622579741</v>
       </c>
       <c r="G222" t="n">
-        <v>0.05112964920091014</v>
+        <v>0.03960521006709856</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0.04750907492906929</v>
+        <v>0.05569710568897827</v>
       </c>
       <c r="B223" t="n">
-        <v>0.04694073918864242</v>
+        <v>0.037048889024654</v>
       </c>
       <c r="C223" t="n">
-        <v>0.08720208096769057</v>
+        <v>0.1687694516656872</v>
       </c>
       <c r="D223" t="n">
-        <v>0.3590642345980079</v>
+        <v>0.295447202173866</v>
       </c>
       <c r="E223" t="n">
-        <v>0.3534867450044775</v>
+        <v>0.3106862568785001</v>
       </c>
       <c r="F223" t="n">
-        <v>0.05466490236461825</v>
+        <v>0.09273107280372278</v>
       </c>
       <c r="G223" t="n">
-        <v>0.05113222294749906</v>
+        <v>0.03962002176459136</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>0.04751360289777667</v>
+        <v>0.05574352971212018</v>
       </c>
       <c r="B224" t="n">
-        <v>0.04694078105713027</v>
+        <v>0.03705226799799082</v>
       </c>
       <c r="C224" t="n">
-        <v>0.08720235137767965</v>
+        <v>0.1686339604185798</v>
       </c>
       <c r="D224" t="n">
-        <v>0.3590794393558386</v>
+        <v>0.2953541827342975</v>
       </c>
       <c r="E224" t="n">
-        <v>0.3534640201258543</v>
+        <v>0.3107284577588298</v>
       </c>
       <c r="F224" t="n">
-        <v>0.05466511655572374</v>
+        <v>0.0928527600150658</v>
       </c>
       <c r="G224" t="n">
-        <v>0.05113468862999929</v>
+        <v>0.03963484136311614</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0.04751787582286768</v>
+        <v>0.0557886240722302</v>
       </c>
       <c r="B225" t="n">
-        <v>0.04694084633996524</v>
+        <v>0.03705526616224797</v>
       </c>
       <c r="C225" t="n">
-        <v>0.0872025566125549</v>
+        <v>0.1685000293866117</v>
       </c>
       <c r="D225" t="n">
-        <v>0.3590942190026032</v>
+        <v>0.295289732405974</v>
       </c>
       <c r="E225" t="n">
-        <v>0.3534419880261153</v>
+        <v>0.3107434721524905</v>
       </c>
       <c r="F225" t="n">
-        <v>0.05466546229482306</v>
+        <v>0.0929732083931331</v>
       </c>
       <c r="G225" t="n">
-        <v>0.05113705190106865</v>
+        <v>0.03964966742731293</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0.0475219072094803</v>
+        <v>0.05583242732595466</v>
       </c>
       <c r="B226" t="n">
-        <v>0.04694093380677172</v>
+        <v>0.03705789042813779</v>
       </c>
       <c r="C226" t="n">
-        <v>0.08720269940954094</v>
+        <v>0.1683678325867929</v>
       </c>
       <c r="D226" t="n">
-        <v>0.3591084405662061</v>
+        <v>0.2952538810735316</v>
       </c>
       <c r="E226" t="n">
-        <v>0.3534207704289816</v>
+        <v>0.310731140615961</v>
       </c>
       <c r="F226" t="n">
-        <v>0.05466593033237355</v>
+        <v>0.09309233185775101</v>
       </c>
       <c r="G226" t="n">
-        <v>0.05113931824664517</v>
+        <v>0.03966449611187122</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0.04752571049347969</v>
+        <v>0.0558749741569818</v>
       </c>
       <c r="B227" t="n">
-        <v>0.0469410420659343</v>
+        <v>0.03706015031912856</v>
       </c>
       <c r="C227" t="n">
-        <v>0.08720278341605429</v>
+        <v>0.1682375149190542</v>
       </c>
       <c r="D227" t="n">
-        <v>0.3591219872059425</v>
+        <v>0.2952456541519516</v>
       </c>
       <c r="E227" t="n">
-        <v>0.3534004729905104</v>
+        <v>0.3106923259383265</v>
       </c>
       <c r="F227" t="n">
-        <v>0.05466651086576315</v>
+        <v>0.09321005910516056</v>
       </c>
       <c r="G227" t="n">
-        <v>0.05114149296231724</v>
+        <v>0.03967932140939671</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>0.0475292989954019</v>
+        <v>0.05591629541166181</v>
       </c>
       <c r="B228" t="n">
-        <v>0.04694116960439701</v>
+        <v>0.03706205791882849</v>
       </c>
       <c r="C228" t="n">
-        <v>0.08720281296298509</v>
+        <v>0.1681091898482605</v>
       </c>
       <c r="D228" t="n">
-        <v>0.3591347590340486</v>
+        <v>0.2952631938088329</v>
       </c>
       <c r="E228" t="n">
-        <v>0.3533811845925881</v>
+        <v>0.3106287927357104</v>
       </c>
       <c r="F228" t="n">
-        <v>0.05466719367461418</v>
+        <v>0.09332633467697996</v>
       </c>
       <c r="G228" t="n">
-        <v>0.0511435811359686</v>
+        <v>0.03969413559972568</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>0.04753268586727865</v>
+        <v>0.05595641828901692</v>
       </c>
       <c r="B229" t="n">
-        <v>0.0469413148286421</v>
+        <v>0.03706362778854881</v>
       </c>
       <c r="C229" t="n">
-        <v>0.0872027928587414</v>
+        <v>0.167982938482922</v>
       </c>
       <c r="D229" t="n">
-        <v>0.3591466733741359</v>
+        <v>0.2953038990781438</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3533629772014689</v>
+        <v>0.3105430667868932</v>
       </c>
       <c r="F229" t="n">
-        <v>0.05466796823648956</v>
+        <v>0.09344111973156892</v>
       </c>
       <c r="G229" t="n">
-        <v>0.05114558763324309</v>
+        <v>0.03970892984290654</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>0.04753588404321276</v>
+        <v>0.05599536662091584</v>
       </c>
       <c r="B230" t="n">
-        <v>0.04694147611027803</v>
+        <v>0.03706487681975888</v>
       </c>
       <c r="C230" t="n">
-        <v>0.0872027282150344</v>
+        <v>0.1678588101408941</v>
       </c>
       <c r="D230" t="n">
-        <v>0.3591576644857762</v>
+        <v>0.2953645777635193</v>
       </c>
       <c r="E230" t="n">
-        <v>0.3533459062166461</v>
+        <v>0.3104382813392663</v>
       </c>
       <c r="F230" t="n">
-        <v>0.05466882383486166</v>
+        <v>0.09355439245606544</v>
       </c>
       <c r="G230" t="n">
-        <v>0.05114751709419305</v>
+        <v>0.03972369485957991</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0.04753890618608094</v>
+        <v>0.0560331612465797</v>
       </c>
       <c r="B231" t="n">
-        <v>0.04694165182754354</v>
+        <v>0.0370658240245537</v>
       </c>
       <c r="C231" t="n">
-        <v>0.08720262429809114</v>
+        <v>0.1677368242334013</v>
       </c>
       <c r="D231" t="n">
-        <v>0.3591676829880595</v>
+        <v>0.295441603808259</v>
       </c>
       <c r="E231" t="n">
-        <v>0.3533300111192245</v>
+        <v>0.3103180169175085</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0546697496487919</v>
+        <v>0.09366614814066018</v>
       </c>
       <c r="G231" t="n">
-        <v>0.05114937393220645</v>
+        <v>0.03973842162903781</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>0.04754176463661197</v>
+        <v>0.05606982043428799</v>
       </c>
       <c r="B232" t="n">
-        <v>0.04694184040350239</v>
+        <v>0.03706649025501237</v>
       </c>
       <c r="C232" t="n">
-        <v>0.08720248640608744</v>
+        <v>0.1676169732988406</v>
       </c>
       <c r="D232" t="n">
-        <v>0.3591766950358398</v>
+        <v>0.2955310743432962</v>
       </c>
       <c r="E232" t="n">
-        <v>0.3533153163472992</v>
+        <v>0.3101861407562515</v>
       </c>
       <c r="F232" t="n">
-        <v>0.05467073483253624</v>
+        <v>0.09377639887517072</v>
       </c>
       <c r="G232" t="n">
-        <v>0.05115116233812063</v>
+        <v>0.03975310203714044</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>0.04754447136542766</v>
+        <v>0.05610536032447668</v>
       </c>
       <c r="B233" t="n">
-        <v>0.04694204033876398</v>
+        <v>0.03706689786255458</v>
       </c>
       <c r="C233" t="n">
-        <v>0.08720231976771155</v>
+        <v>0.1674992269069576</v>
       </c>
       <c r="D233" t="n">
-        <v>0.3591846813339132</v>
+        <v>0.2956289615164462</v>
       </c>
       <c r="E233" t="n">
-        <v>0.3533018323201004</v>
+        <v>0.3100466511355204</v>
       </c>
       <c r="F233" t="n">
-        <v>0.05467176858668681</v>
+        <v>0.09388517284489922</v>
       </c>
       <c r="G233" t="n">
-        <v>0.051152886287398</v>
+        <v>0.03976772940914541</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>0.04754703793053714</v>
+        <v>0.05613979536926651</v>
       </c>
       <c r="B234" t="n">
-        <v>0.04694225023923657</v>
+        <v>0.03706707031228534</v>
       </c>
       <c r="C234" t="n">
-        <v>0.087202129450384</v>
+        <v>0.167383536093196</v>
       </c>
       <c r="D234" t="n">
-        <v>0.3591916360199031</v>
+        <v>0.2957312550116233</v>
       </c>
       <c r="E234" t="n">
-        <v>0.3532895565838279</v>
+        <v>0.3099035311250187</v>
       </c>
       <c r="F234" t="n">
-        <v>0.05467284022541635</v>
+        <v>0.09399251321610901</v>
       </c>
       <c r="G234" t="n">
-        <v>0.0511545495506951</v>
+        <v>0.03978229887250115</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>0.04754947543682819</v>
+        <v>0.05617313875835333</v>
       </c>
       <c r="B235" t="n">
-        <v>0.04694246883074837</v>
+        <v>0.03706703177739362</v>
       </c>
       <c r="C235" t="n">
-        <v>0.08720192030445584</v>
+        <v>0.1672698379812907</v>
       </c>
       <c r="D235" t="n">
-        <v>0.3591975654974813</v>
+        <v>0.2958340919333399</v>
       </c>
       <c r="E235" t="n">
-        <v>0.3532784749984237</v>
+        <v>0.3097606154218141</v>
       </c>
       <c r="F235" t="n">
-        <v>0.05467393923295819</v>
+        <v>0.09409847661091592</v>
       </c>
       <c r="G235" t="n">
-        <v>0.05115615569910284</v>
+        <v>0.03979680751689259</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>0.04755179450519875</v>
+        <v>0.05620540280546776</v>
       </c>
       <c r="B236" t="n">
-        <v>0.04694269497195842</v>
+        <v>0.03706680673164964</v>
       </c>
       <c r="C236" t="n">
-        <v>0.08720169687126815</v>
+        <v>0.1671580602694405</v>
       </c>
       <c r="D236" t="n">
-        <v>0.3592024870757183</v>
+        <v>0.2959338715215703</v>
       </c>
       <c r="E236" t="n">
-        <v>0.3532685631350453</v>
+        <v>0.3096214731827153</v>
       </c>
       <c r="F236" t="n">
-        <v>0.05467505532701383</v>
+        <v>0.09420313116213735</v>
       </c>
       <c r="G236" t="n">
-        <v>0.05115770811379169</v>
+        <v>0.03981125432701925</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>0.04755400524625173</v>
+        <v>0.05623659929516461</v>
       </c>
       <c r="B237" t="n">
-        <v>0.04694292765760343</v>
+        <v>0.03706641955510093</v>
       </c>
       <c r="C237" t="n">
-        <v>0.08720146332860376</v>
+        <v>0.1670481252632095</v>
       </c>
       <c r="D237" t="n">
-        <v>0.3592064276523252</v>
+        <v>0.2960273528549225</v>
       </c>
       <c r="E237" t="n">
-        <v>0.3532597876086174</v>
+        <v>0.3094893089331693</v>
       </c>
       <c r="F237" t="n">
-        <v>0.05467617851476351</v>
+        <v>0.09430655420327475</v>
       </c>
       <c r="G237" t="n">
-        <v>0.05115920999182922</v>
+        <v>0.03982563989515844</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>0.04755611724445243</v>
+        <v>0.05626673982603625</v>
       </c>
       <c r="B238" t="n">
-        <v>0.04694316601701473</v>
+        <v>0.03706589415757081</v>
       </c>
       <c r="C238" t="n">
-        <v>0.08720122343505525</v>
+        <v>0.1669399531983967</v>
       </c>
       <c r="D238" t="n">
-        <v>0.3592094222254121</v>
+        <v>0.2961117343954806</v>
       </c>
       <c r="E238" t="n">
-        <v>0.3532521075713604</v>
+        <v>0.3093668828014659</v>
       </c>
       <c r="F238" t="n">
-        <v>0.05467729915405844</v>
+        <v>0.09440882970028554</v>
       </c>
       <c r="G238" t="n">
-        <v>0.05116066435264277</v>
+        <v>0.03983996592076402</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0.04755813954878801</v>
+        <v>0.05629583607840782</v>
       </c>
       <c r="B239" t="n">
-        <v>0.0469434093071894</v>
+        <v>0.03706525363331185</v>
       </c>
       <c r="C239" t="n">
-        <v>0.08720098048317654</v>
+        <v>0.1668334647620208</v>
       </c>
       <c r="D239" t="n">
-        <v>0.3592115124111036</v>
+        <v>0.2961847145924836</v>
       </c>
       <c r="E239" t="n">
-        <v>0.3532454761931275</v>
+        <v>0.3092564509646914</v>
       </c>
       <c r="F239" t="n">
-        <v>0.05467840801363982</v>
+        <v>0.09451004540269373</v>
       </c>
       <c r="G239" t="n">
-        <v>0.05116207404298565</v>
+        <v>0.03985423456639089</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>0.0475600806642604</v>
+        <v>0.05632390007935233</v>
       </c>
       <c r="B240" t="n">
-        <v>0.04694365689476265</v>
+        <v>0.03706451993881726</v>
       </c>
       <c r="C240" t="n">
-        <v>0.08720073725408781</v>
+        <v>0.1667285826835492</v>
       </c>
       <c r="D240" t="n">
-        <v>0.3592127449664098</v>
+        <v>0.2962445334844975</v>
       </c>
       <c r="E240" t="n">
-        <v>0.3532398421607902</v>
+        <v>0.3091597262200669</v>
       </c>
       <c r="F240" t="n">
-        <v>0.05467949632624771</v>
+        <v>0.09461028989953314</v>
       </c>
       <c r="G240" t="n">
-        <v>0.05116344173344329</v>
+        <v>0.03986844769418375</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>0.04756194855419433</v>
+        <v>0.05635094444916913</v>
       </c>
       <c r="B241" t="n">
-        <v>0.04694390824274675</v>
+        <v>0.03706371359401057</v>
       </c>
       <c r="C241" t="n">
-        <v>0.08720049600163964</v>
+        <v>0.166625232469212</v>
       </c>
       <c r="D241" t="n">
-        <v>0.3592131704264583</v>
+        <v>0.2962899954065016</v>
       </c>
       <c r="E241" t="n">
-        <v>0.3532351510058663</v>
+        <v>0.309077858335728</v>
       </c>
       <c r="F241" t="n">
-        <v>0.05468055584597893</v>
+        <v>0.09470964967915294</v>
       </c>
       <c r="G241" t="n">
-        <v>0.05116476992310197</v>
+        <v>0.03988260606622563</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>0.04756375064488901</v>
+        <v>0.05637698262068423</v>
       </c>
       <c r="B242" t="n">
-        <v>0.04694416288875603</v>
+        <v>0.03706285339828223</v>
       </c>
       <c r="C242" t="n">
-        <v>0.08720025844822597</v>
+        <v>0.1665233423888365</v>
       </c>
       <c r="D242" t="n">
-        <v>0.3592128418135423</v>
+        <v>0.2963204733881101</v>
       </c>
       <c r="E242" t="n">
-        <v>0.353231346364097</v>
+        <v>0.3090114333495387</v>
       </c>
       <c r="F242" t="n">
-        <v>0.05468157890156532</v>
+        <v>0.09480820628937747</v>
       </c>
       <c r="G242" t="n">
-        <v>0.05116606093892404</v>
+        <v>0.03989670856517103</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>0.04756549383241364</v>
+        <v>0.05640202905031968</v>
       </c>
       <c r="B243" t="n">
-        <v>0.04694442043011053</v>
+        <v>0.0370619561793393</v>
       </c>
       <c r="C243" t="n">
-        <v>0.08720002579750785</v>
+        <v>0.1664228428820913</v>
       </c>
       <c r="D243" t="n">
-        <v>0.359211813501061</v>
+        <v>0.2963358961225033</v>
       </c>
       <c r="E243" t="n">
-        <v>0.3532283710484008</v>
+        <v>0.308960490523895</v>
       </c>
       <c r="F243" t="n">
-        <v>0.05468255844720378</v>
+        <v>0.09490603372716071</v>
       </c>
       <c r="G243" t="n">
-        <v>0.05116731694330313</v>
+        <v>0.03991075151469058</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>0.04756718448569595</v>
+        <v>0.05642609941010453</v>
       </c>
       <c r="B244" t="n">
-        <v>0.04694468049279452</v>
+        <v>0.03706103658194164</v>
       </c>
       <c r="C244" t="n">
-        <v>0.08719979877440079</v>
+        <v>0.1663236656817517</v>
       </c>
       <c r="D244" t="n">
-        <v>0.3592101403349645</v>
+        <v>0.2963367187351985</v>
       </c>
       <c r="E244" t="n">
-        <v>0.3532261678847223</v>
+        <v>0.3089245553107084</v>
       </c>
       <c r="F244" t="n">
-        <v>0.05468348809942027</v>
+        <v>0.09500319612090037</v>
       </c>
       <c r="G244" t="n">
-        <v>0.05116853992800761</v>
+        <v>0.03992472815939468</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>0.04756882846136664</v>
+        <v>0.05644921076075494</v>
       </c>
       <c r="B245" t="n">
-        <v>0.04694494272031455</v>
+        <v>0.03706010691189758</v>
       </c>
       <c r="C245" t="n">
-        <v>0.08719957766619142</v>
+        <v>0.1662257428741184</v>
       </c>
       <c r="D245" t="n">
-        <v>0.3592078768584271</v>
+        <v>0.2963238790203143</v>
       </c>
       <c r="E245" t="n">
-        <v>0.3532246803762579</v>
+        <v>0.308902686286136</v>
       </c>
       <c r="F245" t="n">
-        <v>0.05468436218669317</v>
+        <v>0.09509974579351028</v>
       </c>
       <c r="G245" t="n">
-        <v>0.05116973173074874</v>
+        <v>0.03993862835326877</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>0.04757043110883061</v>
+        <v>0.05647138170021768</v>
       </c>
       <c r="B246" t="n">
-        <v>0.04694520675104279</v>
+        <v>0.03705917705612977</v>
       </c>
       <c r="C246" t="n">
-        <v>0.08719936240424955</v>
+        <v>0.1661290061837956</v>
       </c>
       <c r="D246" t="n">
-        <v>0.3592050767059864</v>
+        <v>0.2962987411330143</v>
       </c>
       <c r="E246" t="n">
-        <v>0.3532238532102513</v>
+        <v>0.3088935336911554</v>
       </c>
       <c r="F246" t="n">
-        <v>0.05468517577885459</v>
+        <v>0.09519572174109485</v>
       </c>
       <c r="G246" t="n">
-        <v>0.0511708940407842</v>
+        <v>0.03995243849459247</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>0.04757199727656208</v>
+        <v>0.05649263248123757</v>
       </c>
       <c r="B247" t="n">
-        <v>0.04694547220318308</v>
+        <v>0.03705825449638839</v>
       </c>
       <c r="C247" t="n">
-        <v>0.08719915263598478</v>
+        <v>0.166033386700031</v>
       </c>
       <c r="D247" t="n">
-        <v>0.359201792192642</v>
+        <v>0.296263029114243</v>
       </c>
       <c r="E247" t="n">
-        <v>0.353223632566669</v>
+        <v>0.3088954069358296</v>
       </c>
       <c r="F247" t="n">
-        <v>0.0546859247131869</v>
+        <v>0.09529114854860408</v>
       </c>
       <c r="G247" t="n">
-        <v>0.05117202841177507</v>
+        <v>0.03996614172366617</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>0.04757353131354312</v>
+        <v>0.05651298509087201</v>
       </c>
       <c r="B248" t="n">
-        <v>0.0469457386580893</v>
+        <v>0.03705734442823284</v>
       </c>
       <c r="C248" t="n">
-        <v>0.0871989477993317</v>
+        <v>0.1659388151999261</v>
       </c>
       <c r="D248" t="n">
-        <v>0.3591980740399731</v>
+        <v>0.2962187529165168</v>
       </c>
       <c r="E248" t="n">
-        <v>0.3532239663093027</v>
+        <v>0.308906348240051</v>
       </c>
       <c r="F248" t="n">
-        <v>0.05468660560775022</v>
+        <v>0.09538603574532184</v>
       </c>
       <c r="G248" t="n">
-        <v>0.05117313627201425</v>
+        <v>0.03997971837907936</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>0.04757503707658041</v>
+        <v>0.05653246328672145</v>
       </c>
       <c r="B249" t="n">
-        <v>0.04694600565152565</v>
+        <v>0.03705644998924963</v>
       </c>
       <c r="C249" t="n">
-        <v>0.0871987472023537</v>
+        <v>0.1658452231715831</v>
       </c>
       <c r="D249" t="n">
-        <v>0.3591939711026643</v>
+        <v>0.2961681297902052</v>
       </c>
       <c r="E249" t="n">
-        <v>0.353224804150607</v>
+        <v>0.3089242094912827</v>
       </c>
       <c r="F249" t="n">
-        <v>0.0546872158742194</v>
+        <v>0.09548037758213011</v>
       </c>
       <c r="G249" t="n">
-        <v>0.05117421894204849</v>
+        <v>0.0399931466888277</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>0.04757651793857966</v>
+        <v>0.05655109257934554</v>
       </c>
       <c r="B250" t="n">
-        <v>0.04694627267214108</v>
+        <v>0.0370555725803479</v>
       </c>
       <c r="C250" t="n">
-        <v>0.08719855009713523</v>
+        <v>0.1657525444797339</v>
       </c>
       <c r="D250" t="n">
-        <v>0.3591895302411522</v>
+        <v>0.2961135039733966</v>
       </c>
       <c r="E250" t="n">
-        <v>0.3532260976730724</v>
+        <v>0.3089467295247704</v>
       </c>
       <c r="F250" t="n">
-        <v>0.05468775372180544</v>
+        <v>0.0955741532147438</v>
       </c>
       <c r="G250" t="n">
-        <v>0.05117527765611167</v>
+        <v>0.04000640364766175</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>0.04757797679236045</v>
+        <v>0.05656890016434327</v>
       </c>
       <c r="B251" t="n">
-        <v>0.04694653915164261</v>
+        <v>0.03705471226908669</v>
       </c>
       <c r="C251" t="n">
-        <v>0.08719835575196504</v>
+        <v>0.1656607175995544</v>
       </c>
       <c r="D251" t="n">
-        <v>0.3591847961229917</v>
+        <v>0.2960572675664159</v>
       </c>
       <c r="E251" t="n">
-        <v>0.3532278004649195</v>
+        <v>0.3089716091147214</v>
       </c>
       <c r="F251" t="n">
-        <v>0.05468821814431315</v>
+        <v>0.09566732725985126</v>
       </c>
       <c r="G251" t="n">
-        <v>0.05117631357180232</v>
+        <v>0.04001946602602702</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>0.04757941605951211</v>
+        <v>0.0565859147847082</v>
       </c>
       <c r="B252" t="n">
-        <v>0.04694680446648434</v>
+        <v>0.03705386822747694</v>
       </c>
       <c r="C252" t="n">
-        <v>0.08719816348363019</v>
+        <v>0.1655696882661775</v>
       </c>
       <c r="D252" t="n">
-        <v>0.3591798112165862</v>
+        <v>0.2960017852445669</v>
       </c>
       <c r="E252" t="n">
-        <v>0.3532298680862685</v>
+        <v>0.3089965813662194</v>
       </c>
       <c r="F252" t="n">
-        <v>0.05468860890186424</v>
+        <v>0.09575985068503975</v>
       </c>
       <c r="G252" t="n">
-        <v>0.05117732778565342</v>
+        <v>0.04003231142581155</v>
       </c>
     </row>
   </sheetData>
